--- a/seabird_civ_style_prompts_v3.xlsx
+++ b/seabird_civ_style_prompts_v3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nillnill84/dev/seabird/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90536111-940A-5347-B8D3-DDF2FAC54FE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B6F8EED-BC68-E548-BE0E-00168A760E7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="33600" windowHeight="20400" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1010" uniqueCount="344">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1010" uniqueCount="347">
   <si>
     <t>항목</t>
   </si>
@@ -68,9 +68,6 @@
     <t>국가/시대성이 강한 복식, 금속 장식, 자수, 왕관/터번/관모 등 실루엣을 만드는 요소가 중요.</t>
   </si>
   <si>
-    <t>ornate historical costume, rich cloth folds, metal/jewelry highlights</t>
-  </si>
-  <si>
     <t>조명</t>
   </si>
   <si>
@@ -158,12 +155,6 @@
     <t>한국</t>
   </si>
   <si>
-    <t>Civ-like loading leader, mid-thigh crop, right-side placement, stylized 3D painterly realism, ornate historical costume, hands + props visible, transparent PNG</t>
-  </si>
-  <si>
-    <t>Create a Civilization-style grand strategy leader loading-screen character asset for the Seabird maritime intelligence platform, inspired by the provided reference screenshots but not copying any existing game character. Stylized semi-realistic 3D painterly leader, upper-body to mid-thigh crop, three-quarter pose turned slightly toward the viewer, character placed slightly right-of-center as if standing beside an information panel, hands clearly visible, diplomatic command posture, slightly enlarged expressive head and eyes, polished sculpted face, rich cloth folds, ornate costume details, metal and jewelry highlights, theatrical side key light, warm highlights with cool soft shadows, subtle rim light, crisp silhouette, premium strategy game concept art. Transparent alpha background only, no environment; if any atmosphere is needed, use only faint edge shadow on the character, not a backdrop. Leave 8-10% transparent margin around the silhouette; do not crop head, hands, or props; suitable for a React Civ-style modal character header. Output as vertical 2:3 PNG, 1024x1536, alpha channel. Character: Park Seo-yeon (박서연). Role: 글로벌 컨테이너 선단 선장. Type: fictional modern maritime archetype. Asset filename: ship_container.png. Character-specific direction: Korean woman in her early 40s, global container fleet captain; crisp white naval captain uniform with gold epaulettes and four sleeve stripes; short black hair, calm strategic gaze; hands clasped around a small brass compass and folded global route chart; subtle container-stack motif embroidered on cuffs. Important: make the figure feel like a Civ loading-screen leader: not a normal portrait, not a photorealistic person, not a full-body fashion render. Use maritime intelligence symbols only through costume details, handheld props, badges, embroidery, documents, compasses, charts, or small artifacts.</t>
-  </si>
-  <si>
     <t>opaque background, white background, black background, map background, scenery, port scenery, ship scenery, UI panel, frame, border, text, captions, Korean text, logo, watermark, screenshot, full game interface, bust-only close-up, tiny full-body figure, feet-focused full body, cropped head, cropped hands, hands hidden, extra fingers, fused fingers, deformed hands, duplicated limbs, bad anatomy, distorted face, hyperrealistic photo, anime, chibi, cartoon, flat vector, low-poly, plastic toy, oil canvas texture, overpainted blur, low resolution, dull flat lighting, gore, blood, active combat, copied Civilization character</t>
   </si>
   <si>
@@ -191,9 +182,6 @@
     <t>아랍계 (UAE)</t>
   </si>
   <si>
-    <t>Create a Civilization-style grand strategy leader loading-screen character asset for the Seabird maritime intelligence platform, inspired by the provided reference screenshots but not copying any existing game character. Stylized semi-realistic 3D painterly leader, upper-body to mid-thigh crop, three-quarter pose turned slightly toward the viewer, character placed slightly right-of-center as if standing beside an information panel, hands clearly visible, diplomatic command posture, slightly enlarged expressive head and eyes, polished sculpted face, rich cloth folds, ornate costume details, metal and jewelry highlights, theatrical side key light, warm highlights with cool soft shadows, subtle rim light, crisp silhouette, premium strategy game concept art. Transparent alpha background only, no environment; if any atmosphere is needed, use only faint edge shadow on the character, not a backdrop. Leave 8-10% transparent margin around the silhouette; do not crop head, hands, or props; suitable for a React Civ-style modal character header. Output as vertical 2:3 PNG, 1024x1536, alpha channel. Character: Karim Al-Rashid (카림 알-라시드). Role: 원유 탱커 수석 엔지니어. Type: fictional modern maritime archetype. Asset filename: ship_tanker.png. Character-specific direction: Arab man in his late 40s, oil tanker chief engineer; navy coveralls upgraded into a ceremonial engineer coat with orange safety piping and brass pressure-gauge badges; short gray-flecked beard; one hand holds an oil-route clipboard, the other rests near a brass valve wheel prop. Important: make the figure feel like a Civ loading-screen leader: not a normal portrait, not a photorealistic person, not a full-body fashion render. Use maritime intelligence symbols only through costume details, handheld props, badges, embroidery, documents, compasses, charts, or small artifacts.</t>
-  </si>
-  <si>
     <t>ship_bulk.png</t>
   </si>
   <si>
@@ -212,9 +200,6 @@
     <t>서아프리카계 (세네갈)</t>
   </si>
   <si>
-    <t>Create a Civilization-style grand strategy leader loading-screen character asset for the Seabird maritime intelligence platform, inspired by the provided reference screenshots but not copying any existing game character. Stylized semi-realistic 3D painterly leader, upper-body to mid-thigh crop, three-quarter pose turned slightly toward the viewer, character placed slightly right-of-center as if standing beside an information panel, hands clearly visible, diplomatic command posture, slightly enlarged expressive head and eyes, polished sculpted face, rich cloth folds, ornate costume details, metal and jewelry highlights, theatrical side key light, warm highlights with cool soft shadows, subtle rim light, crisp silhouette, premium strategy game concept art. Transparent alpha background only, no environment; if any atmosphere is needed, use only faint edge shadow on the character, not a backdrop. Leave 8-10% transparent margin around the silhouette; do not crop head, hands, or props; suitable for a React Civ-style modal character header. Output as vertical 2:3 PNG, 1024x1536, alpha channel. Character: Amadou Diallo (아마두 디알로). Role: 벌크선 화물장. Type: fictional modern maritime archetype. Asset filename: ship_bulk.png. Character-specific direction: West African man in his 50s, bulk carrier cargo master; heavy navy work jacket with ochre mineral-dust weathering and gold-edged rank patches; powerful hands holding a miniature ore sample and cargo manifest; wise, steady expression. Important: make the figure feel like a Civ loading-screen leader: not a normal portrait, not a photorealistic person, not a full-body fashion render. Use maritime intelligence symbols only through costume details, handheld props, badges, embroidery, documents, compasses, charts, or small artifacts.</t>
-  </si>
-  <si>
     <t>ship_lng.png</t>
   </si>
   <si>
@@ -233,9 +218,6 @@
     <t>북유럽계 (노르웨이)</t>
   </si>
   <si>
-    <t>Create a Civilization-style grand strategy leader loading-screen character asset for the Seabird maritime intelligence platform, inspired by the provided reference screenshots but not copying any existing game character. Stylized semi-realistic 3D painterly leader, upper-body to mid-thigh crop, three-quarter pose turned slightly toward the viewer, character placed slightly right-of-center as if standing beside an information panel, hands clearly visible, diplomatic command posture, slightly enlarged expressive head and eyes, polished sculpted face, rich cloth folds, ornate costume details, metal and jewelry highlights, theatrical side key light, warm highlights with cool soft shadows, subtle rim light, crisp silhouette, premium strategy game concept art. Transparent alpha background only, no environment; if any atmosphere is needed, use only faint edge shadow on the character, not a backdrop. Leave 8-10% transparent margin around the silhouette; do not crop head, hands, or props; suitable for a React Civ-style modal character header. Output as vertical 2:3 PNG, 1024x1536, alpha channel. Character: Sofia Berg (소피아 베르그). Role: LNG 안전관제 책임자. Type: fictional modern maritime archetype. Asset filename: ship_lng.png. Character-specific direction: Scandinavian woman in her mid-30s, LNG safety-control officer; orange fire-retardant uniform shaped like a formal leader coat, white safety helmet tucked under one arm; icy-blue trim, sensor badge, analytical eyes; holding a cryogenic safety tablet. Important: make the figure feel like a Civ loading-screen leader: not a normal portrait, not a photorealistic person, not a full-body fashion render. Use maritime intelligence symbols only through costume details, handheld props, badges, embroidery, documents, compasses, charts, or small artifacts.</t>
-  </si>
-  <si>
     <t>ship_passenger.png</t>
   </si>
   <si>
@@ -254,9 +236,6 @@
     <t>남아시아계 (인도)</t>
   </si>
   <si>
-    <t>Create a Civilization-style grand strategy leader loading-screen character asset for the Seabird maritime intelligence platform, inspired by the provided reference screenshots but not copying any existing game character. Stylized semi-realistic 3D painterly leader, upper-body to mid-thigh crop, three-quarter pose turned slightly toward the viewer, character placed slightly right-of-center as if standing beside an information panel, hands clearly visible, diplomatic command posture, slightly enlarged expressive head and eyes, polished sculpted face, rich cloth folds, ornate costume details, metal and jewelry highlights, theatrical side key light, warm highlights with cool soft shadows, subtle rim light, crisp silhouette, premium strategy game concept art. Transparent alpha background only, no environment; if any atmosphere is needed, use only faint edge shadow on the character, not a backdrop. Leave 8-10% transparent margin around the silhouette; do not crop head, hands, or props; suitable for a React Civ-style modal character header. Output as vertical 2:3 PNG, 1024x1536, alpha channel. Character: Arjun Mehta (아르준 메타). Role: 크루즈 선장. Type: fictional modern maritime archetype. Asset filename: ship_passenger.png. Character-specific direction: Indian man in his 50s, luxury cruise captain; pristine white dress uniform with four gold stripes, medal ribbons, deep blue sash; salt-and-pepper hair and mustache; one hand holds a folded passenger manifest, the other rests confidently at the waist. Important: make the figure feel like a Civ loading-screen leader: not a normal portrait, not a photorealistic person, not a full-body fashion render. Use maritime intelligence symbols only through costume details, handheld props, badges, embroidery, documents, compasses, charts, or small artifacts.</t>
-  </si>
-  <si>
     <t>ship_fishing.png</t>
   </si>
   <si>
@@ -275,9 +254,6 @@
     <t>동남아시아계 (필리핀)</t>
   </si>
   <si>
-    <t>Create a Civilization-style grand strategy leader loading-screen character asset for the Seabird maritime intelligence platform, inspired by the provided reference screenshots but not copying any existing game character. Stylized semi-realistic 3D painterly leader, upper-body to mid-thigh crop, three-quarter pose turned slightly toward the viewer, character placed slightly right-of-center as if standing beside an information panel, hands clearly visible, diplomatic command posture, slightly enlarged expressive head and eyes, polished sculpted face, rich cloth folds, ornate costume details, metal and jewelry highlights, theatrical side key light, warm highlights with cool soft shadows, subtle rim light, crisp silhouette, premium strategy game concept art. Transparent alpha background only, no environment; if any atmosphere is needed, use only faint edge shadow on the character, not a backdrop. Leave 8-10% transparent margin around the silhouette; do not crop head, hands, or props; suitable for a React Civ-style modal character header. Output as vertical 2:3 PNG, 1024x1536, alpha channel. Character: Maria Santos (마리아 산토스). Role: 원양어선 선장. Type: fictional modern maritime archetype. Asset filename: ship_fishing.png. Character-specific direction: Filipino woman in her 40s, deep-sea fishing captain; weathered orange rain slicker reinterpreted as a dignified sea-leader coat, rubberized cuffs, net-knot brooch; gray-streaked hair tied back; holding a coiled fishing line and small sonar screen. Important: make the figure feel like a Civ loading-screen leader: not a normal portrait, not a photorealistic person, not a full-body fashion render. Use maritime intelligence symbols only through costume details, handheld props, badges, embroidery, documents, compasses, charts, or small artifacts.</t>
-  </si>
-  <si>
     <t>ship_special.png</t>
   </si>
   <si>
@@ -296,9 +272,6 @@
     <t>라틴아메리카계 (칠레)</t>
   </si>
   <si>
-    <t>Create a Civilization-style grand strategy leader loading-screen character asset for the Seabird maritime intelligence platform, inspired by the provided reference screenshots but not copying any existing game character. Stylized semi-realistic 3D painterly leader, upper-body to mid-thigh crop, three-quarter pose turned slightly toward the viewer, character placed slightly right-of-center as if standing beside an information panel, hands clearly visible, diplomatic command posture, slightly enlarged expressive head and eyes, polished sculpted face, rich cloth folds, ornate costume details, metal and jewelry highlights, theatrical side key light, warm highlights with cool soft shadows, subtle rim light, crisp silhouette, premium strategy game concept art. Transparent alpha background only, no environment; if any atmosphere is needed, use only faint edge shadow on the character, not a backdrop. Leave 8-10% transparent margin around the silhouette; do not crop head, hands, or props; suitable for a React Civ-style modal character header. Output as vertical 2:3 PNG, 1024x1536, alpha channel. Character: Juan Carrera (후안 카레라). Role: 해양 구조·특수 작전 지휘관. Type: fictional modern maritime archetype. Asset filename: ship_special.png. Character-specific direction: Latin American man in his 40s, naval rescue and special-operations commander; dark navy tactical uniform with rescue insignia, orange rescue cord, compact radio on chest; intense focused expression; one hand holds a signal flare case, the other a waterproof mission map. Important: make the figure feel like a Civ loading-screen leader: not a normal portrait, not a photorealistic person, not a full-body fashion render. Use maritime intelligence symbols only through costume details, handheld props, badges, embroidery, documents, compasses, charts, or small artifacts.</t>
-  </si>
-  <si>
     <t>ship_other.png</t>
   </si>
   <si>
@@ -317,9 +290,6 @@
     <t>사미족/스칸디나비아</t>
   </si>
   <si>
-    <t>Create a Civilization-style grand strategy leader loading-screen character asset for the Seabird maritime intelligence platform, inspired by the provided reference screenshots but not copying any existing game character. Stylized semi-realistic 3D painterly leader, upper-body to mid-thigh crop, three-quarter pose turned slightly toward the viewer, character placed slightly right-of-center as if standing beside an information panel, hands clearly visible, diplomatic command posture, slightly enlarged expressive head and eyes, polished sculpted face, rich cloth folds, ornate costume details, metal and jewelry highlights, theatrical side key light, warm highlights with cool soft shadows, subtle rim light, crisp silhouette, premium strategy game concept art. Transparent alpha background only, no environment; if any atmosphere is needed, use only faint edge shadow on the character, not a backdrop. Leave 8-10% transparent margin around the silhouette; do not crop head, hands, or props; suitable for a React Civ-style modal character header. Output as vertical 2:3 PNG, 1024x1536, alpha channel. Character: Aina Åberg (아이나 오베르그). Role: 미지 항로 항법사. Type: fictional modern maritime archetype. Asset filename: ship_other.png. Character-specific direction: Sámi-Scandinavian woman in her 30s, navigator of unknown routes; dark teal explorer coat with Sámi-inspired geometric trim, silver compass pendant, pale braided hair; holding an antique astrolabe and a glowing unknown sea-route note. Important: make the figure feel like a Civ loading-screen leader: not a normal portrait, not a photorealistic person, not a full-body fashion render. Use maritime intelligence symbols only through costume details, handheld props, badges, embroidery, documents, compasses, charts, or small artifacts.</t>
-  </si>
-  <si>
     <t>region_suez.png</t>
   </si>
   <si>
@@ -338,9 +308,6 @@
     <t>이집트 제2대 대통령 · 수에즈 국유화 1956</t>
   </si>
   <si>
-    <t>Create a Civilization-style grand strategy leader loading-screen character asset for the Seabird maritime intelligence platform, inspired by the provided reference screenshots but not copying any existing game character. Stylized semi-realistic 3D painterly leader, upper-body to mid-thigh crop, three-quarter pose turned slightly toward the viewer, character placed slightly right-of-center as if standing beside an information panel, hands clearly visible, diplomatic command posture, slightly enlarged expressive head and eyes, polished sculpted face, rich cloth folds, ornate costume details, metal and jewelry highlights, theatrical side key light, warm highlights with cool soft shadows, subtle rim light, crisp silhouette, premium strategy game concept art. Transparent alpha background only, no environment; if any atmosphere is needed, use only faint edge shadow on the character, not a backdrop. Leave 8-10% transparent margin around the silhouette; do not crop head, hands, or props; suitable for a React Civ-style modal character header. Output as vertical 2:3 PNG, 1024x1536, alpha channel. Character: Gamal Abdel Nasser (가말 압델 나세르). Role: 이집트 제2대 대통령 · 수에즈 국유화 1956. Type: respectful historical interpretation for a port or chokepoint region. Asset filename: region_suez.png. Character-specific direction: Gamal Abdel Nasser as a charismatic 1950s Egyptian statesman; khaki military dress uniform with restrained medals, strong brows, confident posture; holding a rolled Suez Canal treaty and brass canal ruler; subtle Egyptian eagle pin. Important: make the figure feel like a Civ loading-screen leader: not a normal portrait, not a photorealistic person, not a full-body fashion render. Use maritime intelligence symbols only through costume details, handheld props, badges, embroidery, documents, compasses, charts, or small artifacts.</t>
-  </si>
-  <si>
     <t>region_malacca.png</t>
   </si>
   <si>
@@ -356,9 +323,6 @@
     <t>말라카 전설의 제독 · 15세기</t>
   </si>
   <si>
-    <t>Create a Civilization-style grand strategy leader loading-screen character asset for the Seabird maritime intelligence platform, inspired by the provided reference screenshots but not copying any existing game character. Stylized semi-realistic 3D painterly leader, upper-body to mid-thigh crop, three-quarter pose turned slightly toward the viewer, character placed slightly right-of-center as if standing beside an information panel, hands clearly visible, diplomatic command posture, slightly enlarged expressive head and eyes, polished sculpted face, rich cloth folds, ornate costume details, metal and jewelry highlights, theatrical side key light, warm highlights with cool soft shadows, subtle rim light, crisp silhouette, premium strategy game concept art. Transparent alpha background only, no environment; if any atmosphere is needed, use only faint edge shadow on the character, not a backdrop. Leave 8-10% transparent margin around the silhouette; do not crop head, hands, or props; suitable for a React Civ-style modal character header. Output as vertical 2:3 PNG, 1024x1536, alpha channel. Character: Hang Tuah (항 투아). Role: 말라카 전설의 제독 · 15세기. Type: respectful historical interpretation for a port or chokepoint region. Asset filename: region_malacca.png. Character-specific direction: Hang Tuah as a legendary Malay admiral; ornate 15th-century Malay warrior attire with gold-thread songket, keris at the belt, wrapped headcloth; one hand near the keris hilt, the other holding a strait navigation scroll; loyal fierce gaze. Important: make the figure feel like a Civ loading-screen leader: not a normal portrait, not a photorealistic person, not a full-body fashion render. Use maritime intelligence symbols only through costume details, handheld props, badges, embroidery, documents, compasses, charts, or small artifacts.</t>
-  </si>
-  <si>
     <t>region_hormuz.png</t>
   </si>
   <si>
@@ -374,9 +338,6 @@
     <t>페르시아 아케메네스 제국 3대 왕 · 기원전 550~486</t>
   </si>
   <si>
-    <t>Create a Civilization-style grand strategy leader loading-screen character asset for the Seabird maritime intelligence platform, inspired by the provided reference screenshots but not copying any existing game character. Stylized semi-realistic 3D painterly leader, upper-body to mid-thigh crop, three-quarter pose turned slightly toward the viewer, character placed slightly right-of-center as if standing beside an information panel, hands clearly visible, diplomatic command posture, slightly enlarged expressive head and eyes, polished sculpted face, rich cloth folds, ornate costume details, metal and jewelry highlights, theatrical side key light, warm highlights with cool soft shadows, subtle rim light, crisp silhouette, premium strategy game concept art. Transparent alpha background only, no environment; if any atmosphere is needed, use only faint edge shadow on the character, not a backdrop. Leave 8-10% transparent margin around the silhouette; do not crop head, hands, or props; suitable for a React Civ-style modal character header. Output as vertical 2:3 PNG, 1024x1536, alpha channel. Character: Darius the Great (다리우스 대왕). Role: 페르시아 아케메네스 제국 3대 왕 · 기원전 550~486. Type: respectful historical interpretation for a port or chokepoint region. Asset filename: region_hormuz.png. Character-specific direction: Darius the Great as an Achaemenid Persian king; elaborate patterned royal robe, tall Persian crown, curled beard with gold ornaments; holding a carved tablet of tribute routes and a small Gulf trade seal; imperial, measured expression. Important: make the figure feel like a Civ loading-screen leader: not a normal portrait, not a photorealistic person, not a full-body fashion render. Use maritime intelligence symbols only through costume details, handheld props, badges, embroidery, documents, compasses, charts, or small artifacts.</t>
-  </si>
-  <si>
     <t>region_panama.png</t>
   </si>
   <si>
@@ -392,9 +353,6 @@
     <t>파나마 최고지도자 · 운하 반환 협상가 1968~1981</t>
   </si>
   <si>
-    <t>Create a Civilization-style grand strategy leader loading-screen character asset for the Seabird maritime intelligence platform, inspired by the provided reference screenshots but not copying any existing game character. Stylized semi-realistic 3D painterly leader, upper-body to mid-thigh crop, three-quarter pose turned slightly toward the viewer, character placed slightly right-of-center as if standing beside an information panel, hands clearly visible, diplomatic command posture, slightly enlarged expressive head and eyes, polished sculpted face, rich cloth folds, ornate costume details, metal and jewelry highlights, theatrical side key light, warm highlights with cool soft shadows, subtle rim light, crisp silhouette, premium strategy game concept art. Transparent alpha background only, no environment; if any atmosphere is needed, use only faint edge shadow on the character, not a backdrop. Leave 8-10% transparent margin around the silhouette; do not crop head, hands, or props; suitable for a React Civ-style modal character header. Output as vertical 2:3 PNG, 1024x1536, alpha channel. Character: Omar Torrijos (오마르 토리호스). Role: 파나마 최고지도자 · 운하 반환 협상가 1968~1981. Type: respectful historical interpretation for a port or chokepoint region. Asset filename: region_panama.png. Character-specific direction: Omar Torrijos as a 1970s Panamanian military leader; olive-green uniform with general insignia, rolled sleeves, populist direct gaze; holding a Panama Canal transfer document and canal-lock schematic. Important: make the figure feel like a Civ loading-screen leader: not a normal portrait, not a photorealistic person, not a full-body fashion render. Use maritime intelligence symbols only through costume details, handheld props, badges, embroidery, documents, compasses, charts, or small artifacts.</t>
-  </si>
-  <si>
     <t>region_dover.png</t>
   </si>
   <si>
@@ -410,9 +368,6 @@
     <t>영국 해군 원수 · 트라팔가르 해전 영웅 1805</t>
   </si>
   <si>
-    <t>Create a Civilization-style grand strategy leader loading-screen character asset for the Seabird maritime intelligence platform, inspired by the provided reference screenshots but not copying any existing game character. Stylized semi-realistic 3D painterly leader, upper-body to mid-thigh crop, three-quarter pose turned slightly toward the viewer, character placed slightly right-of-center as if standing beside an information panel, hands clearly visible, diplomatic command posture, slightly enlarged expressive head and eyes, polished sculpted face, rich cloth folds, ornate costume details, metal and jewelry highlights, theatrical side key light, warm highlights with cool soft shadows, subtle rim light, crisp silhouette, premium strategy game concept art. Transparent alpha background only, no environment; if any atmosphere is needed, use only faint edge shadow on the character, not a backdrop. Leave 8-10% transparent margin around the silhouette; do not crop head, hands, or props; suitable for a React Civ-style modal character header. Output as vertical 2:3 PNG, 1024x1536, alpha channel. Character: Admiral Horatio Nelson (호레이쇼 넬슨 제독). Role: 영국 해군 원수 · 트라팔가르 해전 영웅 1805. Type: respectful historical interpretation for a port or chokepoint region. Asset filename: region_dover.png. Character-specific direction: Admiral Horatio Nelson as a British naval hero; early-1800s Royal Navy dress uniform with gold epaulettes, decorations, empty sleeve detail; telescope under one arm, hand over naval chart; resolute expression. Important: make the figure feel like a Civ loading-screen leader: not a normal portrait, not a photorealistic person, not a full-body fashion render. Use maritime intelligence symbols only through costume details, handheld props, badges, embroidery, documents, compasses, charts, or small artifacts.</t>
-  </si>
-  <si>
     <t>region_korea_strait.png</t>
   </si>
   <si>
@@ -428,9 +383,6 @@
     <t>조선 삼도수군통제사 · 1545~1598</t>
   </si>
   <si>
-    <t>Create a Civilization-style grand strategy leader loading-screen character asset for the Seabird maritime intelligence platform, inspired by the provided reference screenshots but not copying any existing game character. Stylized semi-realistic 3D painterly leader, upper-body to mid-thigh crop, three-quarter pose turned slightly toward the viewer, character placed slightly right-of-center as if standing beside an information panel, hands clearly visible, diplomatic command posture, slightly enlarged expressive head and eyes, polished sculpted face, rich cloth folds, ornate costume details, metal and jewelry highlights, theatrical side key light, warm highlights with cool soft shadows, subtle rim light, crisp silhouette, premium strategy game concept art. Transparent alpha background only, no environment; if any atmosphere is needed, use only faint edge shadow on the character, not a backdrop. Leave 8-10% transparent margin around the silhouette; do not crop head, hands, or props; suitable for a React Civ-style modal character header. Output as vertical 2:3 PNG, 1024x1536, alpha channel. Character: Yi Sun-sin (이순신). Role: 조선 삼도수군통제사 · 1545~1598. Type: respectful historical interpretation for a port or chokepoint region. Asset filename: region_korea_strait.png. Character-specific direction: Yi Sun-sin as a Joseon admiral; ornate Korean commander armor and red command robe, winged helmet, calm uncompromising expression; holding a command baton and compact turtle-ship route map. Important: make the figure feel like a Civ loading-screen leader: not a normal portrait, not a photorealistic person, not a full-body fashion render. Use maritime intelligence symbols only through costume details, handheld props, badges, embroidery, documents, compasses, charts, or small artifacts.</t>
-  </si>
-  <si>
     <t>region_bab_el_mandeb.png</t>
   </si>
   <si>
@@ -446,9 +398,6 @@
     <t>예멘·에티오피아의 전설적 여왕 · 기원전 10세기</t>
   </si>
   <si>
-    <t>Create a Civilization-style grand strategy leader loading-screen character asset for the Seabird maritime intelligence platform, inspired by the provided reference screenshots but not copying any existing game character. Stylized semi-realistic 3D painterly leader, upper-body to mid-thigh crop, three-quarter pose turned slightly toward the viewer, character placed slightly right-of-center as if standing beside an information panel, hands clearly visible, diplomatic command posture, slightly enlarged expressive head and eyes, polished sculpted face, rich cloth folds, ornate costume details, metal and jewelry highlights, theatrical side key light, warm highlights with cool soft shadows, subtle rim light, crisp silhouette, premium strategy game concept art. Transparent alpha background only, no environment; if any atmosphere is needed, use only faint edge shadow on the character, not a backdrop. Leave 8-10% transparent margin around the silhouette; do not crop head, hands, or props; suitable for a React Civ-style modal character header. Output as vertical 2:3 PNG, 1024x1536, alpha channel. Character: Queen of Sheba (시바의 여왕). Role: 예멘·에티오피아의 전설적 여왕 · 기원전 10세기. Type: respectful historical interpretation for a port or chokepoint region. Asset filename: region_bab_el_mandeb.png. Character-specific direction: Queen of Sheba as a legendary Sabaean/Ethiopian maritime-trade queen; ancient royal attire with gold jewelry, layered textiles, sculptural headdress; dark skin, mysterious authority; holding incense resin and a Red Sea trade tablet. Important: make the figure feel like a Civ loading-screen leader: not a normal portrait, not a photorealistic person, not a full-body fashion render. Use maritime intelligence symbols only through costume details, handheld props, badges, embroidery, documents, compasses, charts, or small artifacts.</t>
-  </si>
-  <si>
     <t>region_busan.png</t>
   </si>
   <si>
@@ -467,9 +416,6 @@
     <t>신라 해상왕 · 9세기 동아시아 무역 제패</t>
   </si>
   <si>
-    <t>Create a Civilization-style grand strategy leader loading-screen character asset for the Seabird maritime intelligence platform, inspired by the provided reference screenshots but not copying any existing game character. Stylized semi-realistic 3D painterly leader, upper-body to mid-thigh crop, three-quarter pose turned slightly toward the viewer, character placed slightly right-of-center as if standing beside an information panel, hands clearly visible, diplomatic command posture, slightly enlarged expressive head and eyes, polished sculpted face, rich cloth folds, ornate costume details, metal and jewelry highlights, theatrical side key light, warm highlights with cool soft shadows, subtle rim light, crisp silhouette, premium strategy game concept art. Transparent alpha background only, no environment; if any atmosphere is needed, use only faint edge shadow on the character, not a backdrop. Leave 8-10% transparent margin around the silhouette; do not crop head, hands, or props; suitable for a React Civ-style modal character header. Output as vertical 2:3 PNG, 1024x1536, alpha channel. Character: Jang Bogo (장보고). Role: 신라 해상왕 · 9세기 동아시아 무역 제패. Type: respectful historical interpretation for a port or chokepoint region. Asset filename: region_busan.png. Character-specific direction: Jang Bogo as a Silla maritime trade commander; 9th-century Korean military-trade robes with armor panels, sea-green sash, merchant-seal pendant; holding a folded East Asia trade-route scroll. Important: make the figure feel like a Civ loading-screen leader: not a normal portrait, not a photorealistic person, not a full-body fashion render. Use maritime intelligence symbols only through costume details, handheld props, badges, embroidery, documents, compasses, charts, or small artifacts.</t>
-  </si>
-  <si>
     <t>region_incheon.png</t>
   </si>
   <si>
@@ -485,9 +431,6 @@
     <t>고려 명장 · 귀주대첩으로 거란 격퇴 1019</t>
   </si>
   <si>
-    <t>Create a Civilization-style grand strategy leader loading-screen character asset for the Seabird maritime intelligence platform, inspired by the provided reference screenshots but not copying any existing game character. Stylized semi-realistic 3D painterly leader, upper-body to mid-thigh crop, three-quarter pose turned slightly toward the viewer, character placed slightly right-of-center as if standing beside an information panel, hands clearly visible, diplomatic command posture, slightly enlarged expressive head and eyes, polished sculpted face, rich cloth folds, ornate costume details, metal and jewelry highlights, theatrical side key light, warm highlights with cool soft shadows, subtle rim light, crisp silhouette, premium strategy game concept art. Transparent alpha background only, no environment; if any atmosphere is needed, use only faint edge shadow on the character, not a backdrop. Leave 8-10% transparent margin around the silhouette; do not crop head, hands, or props; suitable for a React Civ-style modal character header. Output as vertical 2:3 PNG, 1024x1536, alpha channel. Character: Gang Gam-chan (강감찬). Role: 고려 명장 · 귀주대첩으로 거란 격퇴 1019. Type: respectful historical interpretation for a port or chokepoint region. Asset filename: region_incheon.png. Character-specific direction: Gang Gam-chan as a Goryeo strategist; formal Goryeo court armor and scholar-general robe, gray beard, disciplined gaze; hands clasped over a defensive map tablet and command tally. Important: make the figure feel like a Civ loading-screen leader: not a normal portrait, not a photorealistic person, not a full-body fashion render. Use maritime intelligence symbols only through costume details, handheld props, badges, embroidery, documents, compasses, charts, or small artifacts.</t>
-  </si>
-  <si>
     <t>region_gwangyang.png</t>
   </si>
   <si>
@@ -503,9 +446,6 @@
     <t>포스코 설립자 · 한국 철강산업의 아버지</t>
   </si>
   <si>
-    <t>Create a Civilization-style grand strategy leader loading-screen character asset for the Seabird maritime intelligence platform, inspired by the provided reference screenshots but not copying any existing game character. Stylized semi-realistic 3D painterly leader, upper-body to mid-thigh crop, three-quarter pose turned slightly toward the viewer, character placed slightly right-of-center as if standing beside an information panel, hands clearly visible, diplomatic command posture, slightly enlarged expressive head and eyes, polished sculpted face, rich cloth folds, ornate costume details, metal and jewelry highlights, theatrical side key light, warm highlights with cool soft shadows, subtle rim light, crisp silhouette, premium strategy game concept art. Transparent alpha background only, no environment; if any atmosphere is needed, use only faint edge shadow on the character, not a backdrop. Leave 8-10% transparent margin around the silhouette; do not crop head, hands, or props; suitable for a React Civ-style modal character header. Output as vertical 2:3 PNG, 1024x1536, alpha channel. Character: Park Tae-joon (박태준). Role: 포스코 설립자 · 한국 철강산업의 아버지. Type: respectful historical interpretation for a port or chokepoint region. Asset filename: region_gwangyang.png. Character-specific direction: Park Tae-joon as a modern industrial founder; dignified 1970s Korean business suit subtly armored with steel-blue lapel shine; holding a steel ingot sample and port-industrial blueprint; visionary but austere. Important: make the figure feel like a Civ loading-screen leader: not a normal portrait, not a photorealistic person, not a full-body fashion render. Use maritime intelligence symbols only through costume details, handheld props, badges, embroidery, documents, compasses, charts, or small artifacts.</t>
-  </si>
-  <si>
     <t>region_singapore.png</t>
   </si>
   <si>
@@ -521,9 +461,6 @@
     <t>싱가포르 초대 총리 · 건국의 아버지 1959~1990</t>
   </si>
   <si>
-    <t>Create a Civilization-style grand strategy leader loading-screen character asset for the Seabird maritime intelligence platform, inspired by the provided reference screenshots but not copying any existing game character. Stylized semi-realistic 3D painterly leader, upper-body to mid-thigh crop, three-quarter pose turned slightly toward the viewer, character placed slightly right-of-center as if standing beside an information panel, hands clearly visible, diplomatic command posture, slightly enlarged expressive head and eyes, polished sculpted face, rich cloth folds, ornate costume details, metal and jewelry highlights, theatrical side key light, warm highlights with cool soft shadows, subtle rim light, crisp silhouette, premium strategy game concept art. Transparent alpha background only, no environment; if any atmosphere is needed, use only faint edge shadow on the character, not a backdrop. Leave 8-10% transparent margin around the silhouette; do not crop head, hands, or props; suitable for a React Civ-style modal character header. Output as vertical 2:3 PNG, 1024x1536, alpha channel. Character: Lee Kuan Yew (리콴유). Role: 싱가포르 초대 총리 · 건국의 아버지 1959~1990. Type: respectful historical interpretation for a port or chokepoint region. Asset filename: region_singapore.png. Character-specific direction: Lee Kuan Yew as a statesman of modern Singapore; immaculate white short-sleeve formal shirt with dark trousers, understated pen and papers; holding a port-city masterplan folder; sharp pragmatic gaze. Important: make the figure feel like a Civ loading-screen leader: not a normal portrait, not a photorealistic person, not a full-body fashion render. Use maritime intelligence symbols only through costume details, handheld props, badges, embroidery, documents, compasses, charts, or small artifacts.</t>
-  </si>
-  <si>
     <t>region_shanghai.png</t>
   </si>
   <si>
@@ -539,9 +476,6 @@
     <t>명나라 대항해사 · 1405~1433년 7차 대원정</t>
   </si>
   <si>
-    <t>Create a Civilization-style grand strategy leader loading-screen character asset for the Seabird maritime intelligence platform, inspired by the provided reference screenshots but not copying any existing game character. Stylized semi-realistic 3D painterly leader, upper-body to mid-thigh crop, three-quarter pose turned slightly toward the viewer, character placed slightly right-of-center as if standing beside an information panel, hands clearly visible, diplomatic command posture, slightly enlarged expressive head and eyes, polished sculpted face, rich cloth folds, ornate costume details, metal and jewelry highlights, theatrical side key light, warm highlights with cool soft shadows, subtle rim light, crisp silhouette, premium strategy game concept art. Transparent alpha background only, no environment; if any atmosphere is needed, use only faint edge shadow on the character, not a backdrop. Leave 8-10% transparent margin around the silhouette; do not crop head, hands, or props; suitable for a React Civ-style modal character header. Output as vertical 2:3 PNG, 1024x1536, alpha channel. Character: Zheng He (정화). Role: 명나라 대항해사 · 1405~1433년 7차 대원정. Type: respectful historical interpretation for a port or chokepoint region. Asset filename: region_shanghai.png. Character-specific direction: Zheng He as a Ming dynasty grand admiral; richly embroidered red-and-gold admiral robe, court hat, powerful seafarer presence; holding a treasure-fleet scroll and nautical compass. Important: make the figure feel like a Civ loading-screen leader: not a normal portrait, not a photorealistic person, not a full-body fashion render. Use maritime intelligence symbols only through costume details, handheld props, badges, embroidery, documents, compasses, charts, or small artifacts.</t>
-  </si>
-  <si>
     <t>region_rotterdam.png</t>
   </si>
   <si>
@@ -557,9 +491,6 @@
     <t>로테르담 출신 인문학자 · 1469~1536</t>
   </si>
   <si>
-    <t>Create a Civilization-style grand strategy leader loading-screen character asset for the Seabird maritime intelligence platform, inspired by the provided reference screenshots but not copying any existing game character. Stylized semi-realistic 3D painterly leader, upper-body to mid-thigh crop, three-quarter pose turned slightly toward the viewer, character placed slightly right-of-center as if standing beside an information panel, hands clearly visible, diplomatic command posture, slightly enlarged expressive head and eyes, polished sculpted face, rich cloth folds, ornate costume details, metal and jewelry highlights, theatrical side key light, warm highlights with cool soft shadows, subtle rim light, crisp silhouette, premium strategy game concept art. Transparent alpha background only, no environment; if any atmosphere is needed, use only faint edge shadow on the character, not a backdrop. Leave 8-10% transparent margin around the silhouette; do not crop head, hands, or props; suitable for a React Civ-style modal character header. Output as vertical 2:3 PNG, 1024x1536, alpha channel. Character: Desiderius Erasmus (에라스무스). Role: 로테르담 출신 인문학자 · 1469~1536. Type: respectful historical interpretation for a port or chokepoint region. Asset filename: region_rotterdam.png. Character-specific direction: Desiderius Erasmus as a Renaissance humanist from Rotterdam; scholar robes with fur trim, soft cap, thoughtful eyes; holding an open book and a tiny brass ship token marking humanist trade routes. Important: make the figure feel like a Civ loading-screen leader: not a normal portrait, not a photorealistic person, not a full-body fashion render. Use maritime intelligence symbols only through costume details, handheld props, badges, embroidery, documents, compasses, charts, or small artifacts.</t>
-  </si>
-  <si>
     <t>region_la_lb.png</t>
   </si>
   <si>
@@ -575,9 +506,6 @@
     <t>미 해군 제독 · 태평양 무역로 개척 1853</t>
   </si>
   <si>
-    <t>Create a Civilization-style grand strategy leader loading-screen character asset for the Seabird maritime intelligence platform, inspired by the provided reference screenshots but not copying any existing game character. Stylized semi-realistic 3D painterly leader, upper-body to mid-thigh crop, three-quarter pose turned slightly toward the viewer, character placed slightly right-of-center as if standing beside an information panel, hands clearly visible, diplomatic command posture, slightly enlarged expressive head and eyes, polished sculpted face, rich cloth folds, ornate costume details, metal and jewelry highlights, theatrical side key light, warm highlights with cool soft shadows, subtle rim light, crisp silhouette, premium strategy game concept art. Transparent alpha background only, no environment; if any atmosphere is needed, use only faint edge shadow on the character, not a backdrop. Leave 8-10% transparent margin around the silhouette; do not crop head, hands, or props; suitable for a React Civ-style modal character header. Output as vertical 2:3 PNG, 1024x1536, alpha channel. Character: Commodore Matthew Perry (매슈 페리 제독). Role: 미 해군 제독 · 태평양 무역로 개척 1853. Type: respectful historical interpretation for a port or chokepoint region. Asset filename: region_la_lb.png. Character-specific direction: Commodore Matthew Perry as a 19th-century U.S. naval officer; dark navy commodore uniform with epaulettes, stern diplomatic expression; holding a naval dispatch and spyglass; maritime trade envoy mood. Important: make the figure feel like a Civ loading-screen leader: not a normal portrait, not a photorealistic person, not a full-body fashion render. Use maritime intelligence symbols only through costume details, handheld props, badges, embroidery, documents, compasses, charts, or small artifacts.</t>
-  </si>
-  <si>
     <t>region_dubai.png</t>
   </si>
   <si>
@@ -593,9 +521,6 @@
     <t>두바이 근대화의 아버지 · 재위 1958~1990</t>
   </si>
   <si>
-    <t>Create a Civilization-style grand strategy leader loading-screen character asset for the Seabird maritime intelligence platform, inspired by the provided reference screenshots but not copying any existing game character. Stylized semi-realistic 3D painterly leader, upper-body to mid-thigh crop, three-quarter pose turned slightly toward the viewer, character placed slightly right-of-center as if standing beside an information panel, hands clearly visible, diplomatic command posture, slightly enlarged expressive head and eyes, polished sculpted face, rich cloth folds, ornate costume details, metal and jewelry highlights, theatrical side key light, warm highlights with cool soft shadows, subtle rim light, crisp silhouette, premium strategy game concept art. Transparent alpha background only, no environment; if any atmosphere is needed, use only faint edge shadow on the character, not a backdrop. Leave 8-10% transparent margin around the silhouette; do not crop head, hands, or props; suitable for a React Civ-style modal character header. Output as vertical 2:3 PNG, 1024x1536, alpha channel. Character: Sheikh Rashid bin Saeed Al Maktoum (라시드 빈 사이드). Role: 두바이 근대화의 아버지 · 재위 1958~1990. Type: respectful historical interpretation for a port or chokepoint region. Asset filename: region_dubai.png. Character-specific direction: Sheikh Rashid bin Saeed Al Maktoum as Dubai's modernization ruler; white kandura, bisht with gold trim, ghutra and agal; holding a harbor development plan and pearl-trade token; warm visionary authority. Important: make the figure feel like a Civ loading-screen leader: not a normal portrait, not a photorealistic person, not a full-body fashion render. Use maritime intelligence symbols only through costume details, handheld props, badges, embroidery, documents, compasses, charts, or small artifacts.</t>
-  </si>
-  <si>
     <t>region_yokohama.png</t>
   </si>
   <si>
@@ -611,9 +536,6 @@
     <t>막말 지사 · 일본 개국·근대화 선구자 1836~1867</t>
   </si>
   <si>
-    <t>Create a Civilization-style grand strategy leader loading-screen character asset for the Seabird maritime intelligence platform, inspired by the provided reference screenshots but not copying any existing game character. Stylized semi-realistic 3D painterly leader, upper-body to mid-thigh crop, three-quarter pose turned slightly toward the viewer, character placed slightly right-of-center as if standing beside an information panel, hands clearly visible, diplomatic command posture, slightly enlarged expressive head and eyes, polished sculpted face, rich cloth folds, ornate costume details, metal and jewelry highlights, theatrical side key light, warm highlights with cool soft shadows, subtle rim light, crisp silhouette, premium strategy game concept art. Transparent alpha background only, no environment; if any atmosphere is needed, use only faint edge shadow on the character, not a backdrop. Leave 8-10% transparent margin around the silhouette; do not crop head, hands, or props; suitable for a React Civ-style modal character header. Output as vertical 2:3 PNG, 1024x1536, alpha channel. Character: Sakamoto Ryoma (사카모토 료마). Role: 막말 지사 · 일본 개국·근대화 선구자 1836~1867. Type: respectful historical interpretation for a port or chokepoint region. Asset filename: region_yokohama.png. Character-specific direction: Sakamoto Ryoma as a Bakumatsu reformer; kimono and haori mixed with early modern maritime elements, sword at side but non-combat pose; holding a trade agreement scroll and compass. Important: make the figure feel like a Civ loading-screen leader: not a normal portrait, not a photorealistic person, not a full-body fashion render. Use maritime intelligence symbols only through costume details, handheld props, badges, embroidery, documents, compasses, charts, or small artifacts.</t>
-  </si>
-  <si>
     <t>region_kobe.png</t>
   </si>
   <si>
@@ -629,9 +551,6 @@
     <t>헤이안 말기 무장 · 효고 항구 개발자 1118~1181</t>
   </si>
   <si>
-    <t>Create a Civilization-style grand strategy leader loading-screen character asset for the Seabird maritime intelligence platform, inspired by the provided reference screenshots but not copying any existing game character. Stylized semi-realistic 3D painterly leader, upper-body to mid-thigh crop, three-quarter pose turned slightly toward the viewer, character placed slightly right-of-center as if standing beside an information panel, hands clearly visible, diplomatic command posture, slightly enlarged expressive head and eyes, polished sculpted face, rich cloth folds, ornate costume details, metal and jewelry highlights, theatrical side key light, warm highlights with cool soft shadows, subtle rim light, crisp silhouette, premium strategy game concept art. Transparent alpha background only, no environment; if any atmosphere is needed, use only faint edge shadow on the character, not a backdrop. Leave 8-10% transparent margin around the silhouette; do not crop head, hands, or props; suitable for a React Civ-style modal character header. Output as vertical 2:3 PNG, 1024x1536, alpha channel. Character: Taira no Kiyomori (타이라노 키요모리). Role: 헤이안 말기 무장 · 효고 항구 개발자 1118~1181. Type: respectful historical interpretation for a port or chokepoint region. Asset filename: region_kobe.png. Character-specific direction: Taira no Kiyomori as a late-Heian warrior leader; ornate samurai court armor with crimson silk layers and formal eboshi; holding a port charter scroll; commanding noble gaze. Important: make the figure feel like a Civ loading-screen leader: not a normal portrait, not a photorealistic person, not a full-body fashion render. Use maritime intelligence symbols only through costume details, handheld props, badges, embroidery, documents, compasses, charts, or small artifacts.</t>
-  </si>
-  <si>
     <t>region_ningbo.png</t>
   </si>
   <si>
@@ -647,9 +566,6 @@
     <t>명나라 해상 무역상 · 동아시아 밀무역의 왕 ?~1559</t>
   </si>
   <si>
-    <t>Create a Civilization-style grand strategy leader loading-screen character asset for the Seabird maritime intelligence platform, inspired by the provided reference screenshots but not copying any existing game character. Stylized semi-realistic 3D painterly leader, upper-body to mid-thigh crop, three-quarter pose turned slightly toward the viewer, character placed slightly right-of-center as if standing beside an information panel, hands clearly visible, diplomatic command posture, slightly enlarged expressive head and eyes, polished sculpted face, rich cloth folds, ornate costume details, metal and jewelry highlights, theatrical side key light, warm highlights with cool soft shadows, subtle rim light, crisp silhouette, premium strategy game concept art. Transparent alpha background only, no environment; if any atmosphere is needed, use only faint edge shadow on the character, not a backdrop. Leave 8-10% transparent margin around the silhouette; do not crop head, hands, or props; suitable for a React Civ-style modal character header. Output as vertical 2:3 PNG, 1024x1536, alpha channel. Character: Wang Zhi (왕직). Role: 명나라 해상 무역상 · 동아시아 밀무역의 왕 ?~1559. Type: respectful historical interpretation for a port or chokepoint region. Asset filename: region_ningbo.png. Character-specific direction: Wang Zhi as a Ming-era maritime trader; layered merchant-warrior robes, discreet armor plates, confident ambiguous smile; holding a ledger, seal, and rolled coastal trade map. Important: make the figure feel like a Civ loading-screen leader: not a normal portrait, not a photorealistic person, not a full-body fashion render. Use maritime intelligence symbols only through costume details, handheld props, badges, embroidery, documents, compasses, charts, or small artifacts.</t>
-  </si>
-  <si>
     <t>region_shenzhen.png</t>
   </si>
   <si>
@@ -665,9 +581,6 @@
     <t>중국 최고 지도자 · 개혁개방·선전 경제특구 창설 1904~1997</t>
   </si>
   <si>
-    <t>Create a Civilization-style grand strategy leader loading-screen character asset for the Seabird maritime intelligence platform, inspired by the provided reference screenshots but not copying any existing game character. Stylized semi-realistic 3D painterly leader, upper-body to mid-thigh crop, three-quarter pose turned slightly toward the viewer, character placed slightly right-of-center as if standing beside an information panel, hands clearly visible, diplomatic command posture, slightly enlarged expressive head and eyes, polished sculpted face, rich cloth folds, ornate costume details, metal and jewelry highlights, theatrical side key light, warm highlights with cool soft shadows, subtle rim light, crisp silhouette, premium strategy game concept art. Transparent alpha background only, no environment; if any atmosphere is needed, use only faint edge shadow on the character, not a backdrop. Leave 8-10% transparent margin around the silhouette; do not crop head, hands, or props; suitable for a React Civ-style modal character header. Output as vertical 2:3 PNG, 1024x1536, alpha channel. Character: Deng Xiaoping (덩샤오핑). Role: 중국 최고 지도자 · 개혁개방·선전 경제특구 창설 1904~1997. Type: respectful historical interpretation for a port or chokepoint region. Asset filename: region_shenzhen.png. Character-specific direction: Deng Xiaoping as a reform-era Chinese leader; simple gray Zhongshan suit, elder strategist posture; holding a special economic zone blueprint and small abacus; pragmatic gaze. Important: make the figure feel like a Civ loading-screen leader: not a normal portrait, not a photorealistic person, not a full-body fashion render. Use maritime intelligence symbols only through costume details, handheld props, badges, embroidery, documents, compasses, charts, or small artifacts.</t>
-  </si>
-  <si>
     <t>region_hongkong.png</t>
   </si>
   <si>
@@ -683,9 +596,6 @@
     <t>청나라 흠차대신 · 아편전쟁 저항의 영웅 1785~1850</t>
   </si>
   <si>
-    <t>Create a Civilization-style grand strategy leader loading-screen character asset for the Seabird maritime intelligence platform, inspired by the provided reference screenshots but not copying any existing game character. Stylized semi-realistic 3D painterly leader, upper-body to mid-thigh crop, three-quarter pose turned slightly toward the viewer, character placed slightly right-of-center as if standing beside an information panel, hands clearly visible, diplomatic command posture, slightly enlarged expressive head and eyes, polished sculpted face, rich cloth folds, ornate costume details, metal and jewelry highlights, theatrical side key light, warm highlights with cool soft shadows, subtle rim light, crisp silhouette, premium strategy game concept art. Transparent alpha background only, no environment; if any atmosphere is needed, use only faint edge shadow on the character, not a backdrop. Leave 8-10% transparent margin around the silhouette; do not crop head, hands, or props; suitable for a React Civ-style modal character header. Output as vertical 2:3 PNG, 1024x1536, alpha channel. Character: Lin Zexu (린쩌쉬). Role: 청나라 흠차대신 · 아편전쟁 저항의 영웅 1785~1850. Type: respectful historical interpretation for a port or chokepoint region. Asset filename: region_hongkong.png. Character-specific direction: Lin Zexu as a Qing commissioner; formal Qing official robe with rank badge, mandarin hat, stern moral expression; holding an imperial edict and port-control ledger. Important: make the figure feel like a Civ loading-screen leader: not a normal portrait, not a photorealistic person, not a full-body fashion render. Use maritime intelligence symbols only through costume details, handheld props, badges, embroidery, documents, compasses, charts, or small artifacts.</t>
-  </si>
-  <si>
     <t>region_vladivostok.png</t>
   </si>
   <si>
@@ -701,9 +611,6 @@
     <t>러시아 동시베리아 총독 · 블라디보스토크 창건 1809~1881</t>
   </si>
   <si>
-    <t>Create a Civilization-style grand strategy leader loading-screen character asset for the Seabird maritime intelligence platform, inspired by the provided reference screenshots but not copying any existing game character. Stylized semi-realistic 3D painterly leader, upper-body to mid-thigh crop, three-quarter pose turned slightly toward the viewer, character placed slightly right-of-center as if standing beside an information panel, hands clearly visible, diplomatic command posture, slightly enlarged expressive head and eyes, polished sculpted face, rich cloth folds, ornate costume details, metal and jewelry highlights, theatrical side key light, warm highlights with cool soft shadows, subtle rim light, crisp silhouette, premium strategy game concept art. Transparent alpha background only, no environment; if any atmosphere is needed, use only faint edge shadow on the character, not a backdrop. Leave 8-10% transparent margin around the silhouette; do not crop head, hands, or props; suitable for a React Civ-style modal character header. Output as vertical 2:3 PNG, 1024x1536, alpha channel. Character: Nikolai Muravyov-Amursky (무라비요프-아무르스키). Role: 러시아 동시베리아 총독 · 블라디보스토크 창건 1809~1881. Type: respectful historical interpretation for a port or chokepoint region. Asset filename: region_vladivostok.png. Character-specific direction: Nikolai Muravyov-Amursky as a Russian Far East governor; 19th-century imperial military coat with fur collar and decorations; holding an Amur-region map and maritime survey instrument. Important: make the figure feel like a Civ loading-screen leader: not a normal portrait, not a photorealistic person, not a full-body fashion render. Use maritime intelligence symbols only through costume details, handheld props, badges, embroidery, documents, compasses, charts, or small artifacts.</t>
-  </si>
-  <si>
     <t>region_portklang.png</t>
   </si>
   <si>
@@ -719,9 +626,6 @@
     <t>말라카 술탄국 창건자 · 동남아 무역 제국 1344~1414</t>
   </si>
   <si>
-    <t>Create a Civilization-style grand strategy leader loading-screen character asset for the Seabird maritime intelligence platform, inspired by the provided reference screenshots but not copying any existing game character. Stylized semi-realistic 3D painterly leader, upper-body to mid-thigh crop, three-quarter pose turned slightly toward the viewer, character placed slightly right-of-center as if standing beside an information panel, hands clearly visible, diplomatic command posture, slightly enlarged expressive head and eyes, polished sculpted face, rich cloth folds, ornate costume details, metal and jewelry highlights, theatrical side key light, warm highlights with cool soft shadows, subtle rim light, crisp silhouette, premium strategy game concept art. Transparent alpha background only, no environment; if any atmosphere is needed, use only faint edge shadow on the character, not a backdrop. Leave 8-10% transparent margin around the silhouette; do not crop head, hands, or props; suitable for a React Civ-style modal character header. Output as vertical 2:3 PNG, 1024x1536, alpha channel. Character: Parameswara (파라메스와라). Role: 말라카 술탄국 창건자 · 동남아 무역 제국 1344~1414. Type: respectful historical interpretation for a port or chokepoint region. Asset filename: region_portklang.png. Character-specific direction: Parameswara as founder of the Malacca Sultanate; royal Malay attire with gold songket, ceremonial kris, jeweled headgear; holding a strait trade seal and diplomatic scroll. Important: make the figure feel like a Civ loading-screen leader: not a normal portrait, not a photorealistic person, not a full-body fashion render. Use maritime intelligence symbols only through costume details, handheld props, badges, embroidery, documents, compasses, charts, or small artifacts.</t>
-  </si>
-  <si>
     <t>region_mumbai.png</t>
   </si>
   <si>
@@ -737,9 +641,6 @@
     <t>마라타 제국 창건자 · 인도 최초 근대 해군 건설 1630~1680</t>
   </si>
   <si>
-    <t>Create a Civilization-style grand strategy leader loading-screen character asset for the Seabird maritime intelligence platform, inspired by the provided reference screenshots but not copying any existing game character. Stylized semi-realistic 3D painterly leader, upper-body to mid-thigh crop, three-quarter pose turned slightly toward the viewer, character placed slightly right-of-center as if standing beside an information panel, hands clearly visible, diplomatic command posture, slightly enlarged expressive head and eyes, polished sculpted face, rich cloth folds, ornate costume details, metal and jewelry highlights, theatrical side key light, warm highlights with cool soft shadows, subtle rim light, crisp silhouette, premium strategy game concept art. Transparent alpha background only, no environment; if any atmosphere is needed, use only faint edge shadow on the character, not a backdrop. Leave 8-10% transparent margin around the silhouette; do not crop head, hands, or props; suitable for a React Civ-style modal character header. Output as vertical 2:3 PNG, 1024x1536, alpha channel. Character: Chhatrapati Shivaji Maharaj (시바지 마하라지). Role: 마라타 제국 창건자 · 인도 최초 근대 해군 건설 1630~1680. Type: respectful historical interpretation for a port or chokepoint region. Asset filename: region_mumbai.png. Character-specific direction: Chhatrapati Shivaji Maharaj as a Maratha founder and naval builder; saffron turban, pearl ornaments, armored royal robe; holding a naval fort plan and curved sword lowered in ceremonial pose. Important: make the figure feel like a Civ loading-screen leader: not a normal portrait, not a photorealistic person, not a full-body fashion render. Use maritime intelligence symbols only through costume details, handheld props, badges, embroidery, documents, compasses, charts, or small artifacts.</t>
-  </si>
-  <si>
     <t>region_hamburg.png</t>
   </si>
   <si>
@@ -755,9 +656,6 @@
     <t>작센·바이에른 공작 · 함부르크 항만 창건 1129~1195</t>
   </si>
   <si>
-    <t>Create a Civilization-style grand strategy leader loading-screen character asset for the Seabird maritime intelligence platform, inspired by the provided reference screenshots but not copying any existing game character. Stylized semi-realistic 3D painterly leader, upper-body to mid-thigh crop, three-quarter pose turned slightly toward the viewer, character placed slightly right-of-center as if standing beside an information panel, hands clearly visible, diplomatic command posture, slightly enlarged expressive head and eyes, polished sculpted face, rich cloth folds, ornate costume details, metal and jewelry highlights, theatrical side key light, warm highlights with cool soft shadows, subtle rim light, crisp silhouette, premium strategy game concept art. Transparent alpha background only, no environment; if any atmosphere is needed, use only faint edge shadow on the character, not a backdrop. Leave 8-10% transparent margin around the silhouette; do not crop head, hands, or props; suitable for a React Civ-style modal character header. Output as vertical 2:3 PNG, 1024x1536, alpha channel. Character: Henry the Lion (사자공 하인리히). Role: 작센·바이에른 공작 · 함부르크 항만 창건 1129~1195. Type: respectful historical interpretation for a port or chokepoint region. Asset filename: region_hamburg.png. Character-specific direction: Henry the Lion as a medieval Saxon-Bavarian duke; chainmail under a noble cloak, lion emblem brooch, golden hair; holding a city charter and harbor key. Important: make the figure feel like a Civ loading-screen leader: not a normal portrait, not a photorealistic person, not a full-body fashion render. Use maritime intelligence symbols only through costume details, handheld props, badges, embroidery, documents, compasses, charts, or small artifacts.</t>
-  </si>
-  <si>
     <t>region_newyork.png</t>
   </si>
   <si>
@@ -773,9 +671,6 @@
     <t>미국 초대 재무장관 · 뉴욕 금융·무역 체계 설계 1755~1804</t>
   </si>
   <si>
-    <t>Create a Civilization-style grand strategy leader loading-screen character asset for the Seabird maritime intelligence platform, inspired by the provided reference screenshots but not copying any existing game character. Stylized semi-realistic 3D painterly leader, upper-body to mid-thigh crop, three-quarter pose turned slightly toward the viewer, character placed slightly right-of-center as if standing beside an information panel, hands clearly visible, diplomatic command posture, slightly enlarged expressive head and eyes, polished sculpted face, rich cloth folds, ornate costume details, metal and jewelry highlights, theatrical side key light, warm highlights with cool soft shadows, subtle rim light, crisp silhouette, premium strategy game concept art. Transparent alpha background only, no environment; if any atmosphere is needed, use only faint edge shadow on the character, not a backdrop. Leave 8-10% transparent margin around the silhouette; do not crop head, hands, or props; suitable for a React Civ-style modal character header. Output as vertical 2:3 PNG, 1024x1536, alpha channel. Character: Alexander Hamilton (알렉산더 해밀턴). Role: 미국 초대 재무장관 · 뉴욕 금융·무역 체계 설계 1755~1804. Type: respectful historical interpretation for a port or chokepoint region. Asset filename: region_newyork.png. Character-specific direction: Alexander Hamilton as an American finance architect; late-18th-century formal coat, waistcoat, cravat; holding a ledger of customs revenue and quill; intense, calculating gaze. Important: make the figure feel like a Civ loading-screen leader: not a normal portrait, not a photorealistic person, not a full-body fashion render. Use maritime intelligence symbols only through costume details, handheld props, badges, embroidery, documents, compasses, charts, or small artifacts.</t>
-  </si>
-  <si>
     <t>region_guangzhou.png</t>
   </si>
   <si>
@@ -791,9 +686,6 @@
     <t>중화민국 임시대총통 · 중국 근대 혁명의 아버지 1866~1925</t>
   </si>
   <si>
-    <t>Create a Civilization-style grand strategy leader loading-screen character asset for the Seabird maritime intelligence platform, inspired by the provided reference screenshots but not copying any existing game character. Stylized semi-realistic 3D painterly leader, upper-body to mid-thigh crop, three-quarter pose turned slightly toward the viewer, character placed slightly right-of-center as if standing beside an information panel, hands clearly visible, diplomatic command posture, slightly enlarged expressive head and eyes, polished sculpted face, rich cloth folds, ornate costume details, metal and jewelry highlights, theatrical side key light, warm highlights with cool soft shadows, subtle rim light, crisp silhouette, premium strategy game concept art. Transparent alpha background only, no environment; if any atmosphere is needed, use only faint edge shadow on the character, not a backdrop. Leave 8-10% transparent margin around the silhouette; do not crop head, hands, or props; suitable for a React Civ-style modal character header. Output as vertical 2:3 PNG, 1024x1536, alpha channel. Character: Sun Yat-sen (쑨원). Role: 중화민국 임시대총통 · 중국 근대 혁명의 아버지 1866~1925. Type: respectful historical interpretation for a port or chokepoint region. Asset filename: region_guangzhou.png. Character-specific direction: Sun Yat-sen as a modern revolutionary statesman; dark Zhongshan suit, composed posture; holding a republic document and maritime customs paper; idealistic determined expression. Important: make the figure feel like a Civ loading-screen leader: not a normal portrait, not a photorealistic person, not a full-body fashion render. Use maritime intelligence symbols only through costume details, handheld props, badges, embroidery, documents, compasses, charts, or small artifacts.</t>
-  </si>
-  <si>
     <t>region_qingdao.png</t>
   </si>
   <si>
@@ -809,9 +701,6 @@
     <t>주나라 개국공신 · 제나라(산둥) 시조 기원전 11세기</t>
   </si>
   <si>
-    <t>Create a Civilization-style grand strategy leader loading-screen character asset for the Seabird maritime intelligence platform, inspired by the provided reference screenshots but not copying any existing game character. Stylized semi-realistic 3D painterly leader, upper-body to mid-thigh crop, three-quarter pose turned slightly toward the viewer, character placed slightly right-of-center as if standing beside an information panel, hands clearly visible, diplomatic command posture, slightly enlarged expressive head and eyes, polished sculpted face, rich cloth folds, ornate costume details, metal and jewelry highlights, theatrical side key light, warm highlights with cool soft shadows, subtle rim light, crisp silhouette, premium strategy game concept art. Transparent alpha background only, no environment; if any atmosphere is needed, use only faint edge shadow on the character, not a backdrop. Leave 8-10% transparent margin around the silhouette; do not crop head, hands, or props; suitable for a React Civ-style modal character header. Output as vertical 2:3 PNG, 1024x1536, alpha channel. Character: Jiang Taigong (강태공). Role: 주나라 개국공신 · 제나라(산둥) 시조 기원전 11세기. Type: respectful historical interpretation for a port or chokepoint region. Asset filename: region_qingdao.png. Character-specific direction: Jiang Taigong as an ancient strategist; Zhou-era robes, white beard, serene eyes; holding a bamboo strategy slip and fishing rod fragment as symbolic prop. Important: make the figure feel like a Civ loading-screen leader: not a normal portrait, not a photorealistic person, not a full-body fashion render. Use maritime intelligence symbols only through costume details, handheld props, badges, embroidery, documents, compasses, charts, or small artifacts.</t>
-  </si>
-  <si>
     <t>region_tianjin.png</t>
   </si>
   <si>
@@ -827,9 +716,6 @@
     <t>청나라 직예총독 · 양무운동 주도 1823~1901</t>
   </si>
   <si>
-    <t>Create a Civilization-style grand strategy leader loading-screen character asset for the Seabird maritime intelligence platform, inspired by the provided reference screenshots but not copying any existing game character. Stylized semi-realistic 3D painterly leader, upper-body to mid-thigh crop, three-quarter pose turned slightly toward the viewer, character placed slightly right-of-center as if standing beside an information panel, hands clearly visible, diplomatic command posture, slightly enlarged expressive head and eyes, polished sculpted face, rich cloth folds, ornate costume details, metal and jewelry highlights, theatrical side key light, warm highlights with cool soft shadows, subtle rim light, crisp silhouette, premium strategy game concept art. Transparent alpha background only, no environment; if any atmosphere is needed, use only faint edge shadow on the character, not a backdrop. Leave 8-10% transparent margin around the silhouette; do not crop head, hands, or props; suitable for a React Civ-style modal character header. Output as vertical 2:3 PNG, 1024x1536, alpha channel. Character: Li Hongzhang (이홍장). Role: 청나라 직예총독 · 양무운동 주도 1823~1901. Type: respectful historical interpretation for a port or chokepoint region. Asset filename: region_tianjin.png. Character-specific direction: Li Hongzhang as a Qing reform statesman; formal Qing official robe with high-rank badge, mandarin hat, tired but shrewd gaze; holding a treaty folder and modernization blueprint. Important: make the figure feel like a Civ loading-screen leader: not a normal portrait, not a photorealistic person, not a full-body fashion render. Use maritime intelligence symbols only through costume details, handheld props, badges, embroidery, documents, compasses, charts, or small artifacts.</t>
-  </si>
-  <si>
     <t>region_antwerp.png</t>
   </si>
   <si>
@@ -845,9 +731,6 @@
     <t>앤트워프 출신 바로크 화가 · 외교관 1577~1640</t>
   </si>
   <si>
-    <t>Create a Civilization-style grand strategy leader loading-screen character asset for the Seabird maritime intelligence platform, inspired by the provided reference screenshots but not copying any existing game character. Stylized semi-realistic 3D painterly leader, upper-body to mid-thigh crop, three-quarter pose turned slightly toward the viewer, character placed slightly right-of-center as if standing beside an information panel, hands clearly visible, diplomatic command posture, slightly enlarged expressive head and eyes, polished sculpted face, rich cloth folds, ornate costume details, metal and jewelry highlights, theatrical side key light, warm highlights with cool soft shadows, subtle rim light, crisp silhouette, premium strategy game concept art. Transparent alpha background only, no environment; if any atmosphere is needed, use only faint edge shadow on the character, not a backdrop. Leave 8-10% transparent margin around the silhouette; do not crop head, hands, or props; suitable for a React Civ-style modal character header. Output as vertical 2:3 PNG, 1024x1536, alpha channel. Character: Peter Paul Rubens (피터 폴 루벤스). Role: 앤트워프 출신 바로크 화가 · 외교관 1577~1640. Type: respectful historical interpretation for a port or chokepoint region. Asset filename: region_antwerp.png. Character-specific direction: Peter Paul Rubens as a Baroque painter-diplomat; black doublet, white collar, painterly cloak; holding a diplomatic letter and small brush; warm confident expression. Important: make the figure feel like a Civ loading-screen leader: not a normal portrait, not a photorealistic person, not a full-body fashion render. Use maritime intelligence symbols only through costume details, handheld props, badges, embroidery, documents, compasses, charts, or small artifacts.</t>
-  </si>
-  <si>
     <t>region_tanjung_pelepas.png</t>
   </si>
   <si>
@@ -863,9 +746,6 @@
     <t>조호르 술탄국 아버지 · 근대 조호르 창건 1833~1895</t>
   </si>
   <si>
-    <t>Create a Civilization-style grand strategy leader loading-screen character asset for the Seabird maritime intelligence platform, inspired by the provided reference screenshots but not copying any existing game character. Stylized semi-realistic 3D painterly leader, upper-body to mid-thigh crop, three-quarter pose turned slightly toward the viewer, character placed slightly right-of-center as if standing beside an information panel, hands clearly visible, diplomatic command posture, slightly enlarged expressive head and eyes, polished sculpted face, rich cloth folds, ornate costume details, metal and jewelry highlights, theatrical side key light, warm highlights with cool soft shadows, subtle rim light, crisp silhouette, premium strategy game concept art. Transparent alpha background only, no environment; if any atmosphere is needed, use only faint edge shadow on the character, not a backdrop. Leave 8-10% transparent margin around the silhouette; do not crop head, hands, or props; suitable for a React Civ-style modal character header. Output as vertical 2:3 PNG, 1024x1536, alpha channel. Character: Sultan Abu Bakar of Johor (술탄 아부 바카르). Role: 조호르 술탄국 아버지 · 근대 조호르 창건 1833~1895. Type: respectful historical interpretation for a port or chokepoint region. Asset filename: region_tanjung_pelepas.png. Character-specific direction: Sultan Abu Bakar of Johor as a modernizing Malay ruler; elegant Johor royal attire with sash and medals, songkok; holding a port-development decree and maritime compass. Important: make the figure feel like a Civ loading-screen leader: not a normal portrait, not a photorealistic person, not a full-body fashion render. Use maritime intelligence symbols only through costume details, handheld props, badges, embroidery, documents, compasses, charts, or small artifacts.</t>
-  </si>
-  <si>
     <t>region_xiamen.png</t>
   </si>
   <si>
@@ -881,9 +761,6 @@
     <t>명나라 충신 · 샤먼 기반 해상 왕국 건설 1624~1662</t>
   </si>
   <si>
-    <t>Create a Civilization-style grand strategy leader loading-screen character asset for the Seabird maritime intelligence platform, inspired by the provided reference screenshots but not copying any existing game character. Stylized semi-realistic 3D painterly leader, upper-body to mid-thigh crop, three-quarter pose turned slightly toward the viewer, character placed slightly right-of-center as if standing beside an information panel, hands clearly visible, diplomatic command posture, slightly enlarged expressive head and eyes, polished sculpted face, rich cloth folds, ornate costume details, metal and jewelry highlights, theatrical side key light, warm highlights with cool soft shadows, subtle rim light, crisp silhouette, premium strategy game concept art. Transparent alpha background only, no environment; if any atmosphere is needed, use only faint edge shadow on the character, not a backdrop. Leave 8-10% transparent margin around the silhouette; do not crop head, hands, or props; suitable for a React Civ-style modal character header. Output as vertical 2:3 PNG, 1024x1536, alpha channel. Character: Koxinga (Zheng Chenggong) (정성공). Role: 명나라 충신 · 샤먼 기반 해상 왕국 건설 1624~1662. Type: respectful historical interpretation for a port or chokepoint region. Asset filename: region_xiamen.png. Character-specific direction: Koxinga / Zheng Chenggong as a Ming loyalist maritime commander; Chinese military robes with armor, red cape, determined gaze; holding a command fan and coastal fortress chart. Important: make the figure feel like a Civ loading-screen leader: not a normal portrait, not a photorealistic person, not a full-body fashion render. Use maritime intelligence symbols only through costume details, handheld props, badges, embroidery, documents, compasses, charts, or small artifacts.</t>
-  </si>
-  <si>
     <t>region_kaohsiung.png</t>
   </si>
   <si>
@@ -899,9 +776,6 @@
     <t>중화민국 제9대 총통 · 대만 민주화의 아버지 1923~2020</t>
   </si>
   <si>
-    <t>Create a Civilization-style grand strategy leader loading-screen character asset for the Seabird maritime intelligence platform, inspired by the provided reference screenshots but not copying any existing game character. Stylized semi-realistic 3D painterly leader, upper-body to mid-thigh crop, three-quarter pose turned slightly toward the viewer, character placed slightly right-of-center as if standing beside an information panel, hands clearly visible, diplomatic command posture, slightly enlarged expressive head and eyes, polished sculpted face, rich cloth folds, ornate costume details, metal and jewelry highlights, theatrical side key light, warm highlights with cool soft shadows, subtle rim light, crisp silhouette, premium strategy game concept art. Transparent alpha background only, no environment; if any atmosphere is needed, use only faint edge shadow on the character, not a backdrop. Leave 8-10% transparent margin around the silhouette; do not crop head, hands, or props; suitable for a React Civ-style modal character header. Output as vertical 2:3 PNG, 1024x1536, alpha channel. Character: Lee Teng-hui (리덩후이). Role: 중화민국 제9대 총통 · 대만 민주화의 아버지 1923~2020. Type: respectful historical interpretation for a port or chokepoint region. Asset filename: region_kaohsiung.png. Character-specific direction: Lee Teng-hui as Taiwan democratization statesman; dark suit, modest tie, elder statesman expression; holding a democratic reform document and port-economy chart. Important: make the figure feel like a Civ loading-screen leader: not a normal portrait, not a photorealistic person, not a full-body fashion render. Use maritime intelligence symbols only through costume details, handheld props, badges, embroidery, documents, compasses, charts, or small artifacts.</t>
-  </si>
-  <si>
     <t>region_laem_chabang.png</t>
   </si>
   <si>
@@ -917,9 +791,6 @@
     <t>태국 국왕 라마 5세 · 근대화 개혁 1853~1910</t>
   </si>
   <si>
-    <t>Create a Civilization-style grand strategy leader loading-screen character asset for the Seabird maritime intelligence platform, inspired by the provided reference screenshots but not copying any existing game character. Stylized semi-realistic 3D painterly leader, upper-body to mid-thigh crop, three-quarter pose turned slightly toward the viewer, character placed slightly right-of-center as if standing beside an information panel, hands clearly visible, diplomatic command posture, slightly enlarged expressive head and eyes, polished sculpted face, rich cloth folds, ornate costume details, metal and jewelry highlights, theatrical side key light, warm highlights with cool soft shadows, subtle rim light, crisp silhouette, premium strategy game concept art. Transparent alpha background only, no environment; if any atmosphere is needed, use only faint edge shadow on the character, not a backdrop. Leave 8-10% transparent margin around the silhouette; do not crop head, hands, or props; suitable for a React Civ-style modal character header. Output as vertical 2:3 PNG, 1024x1536, alpha channel. Character: King Chulalongkorn (Rama V) (쭐랄롱꼰 대왕). Role: 태국 국왕 라마 5세 · 근대화 개혁 1853~1910. Type: respectful historical interpretation for a port or chokepoint region. Asset filename: region_laem_chabang.png. Character-specific direction: King Chulalongkorn / Rama V as a Thai modernizing monarch; ornate Thai royal military uniform with decorations and sash; holding a railway-port modernization plan. Important: make the figure feel like a Civ loading-screen leader: not a normal portrait, not a photorealistic person, not a full-body fashion render. Use maritime intelligence symbols only through costume details, handheld props, badges, embroidery, documents, compasses, charts, or small artifacts.</t>
-  </si>
-  <si>
     <t>region_jakarta.png</t>
   </si>
   <si>
@@ -935,9 +806,6 @@
     <t>인도네시아 초대 대통령 · 독립운동 지도자 1901~1970</t>
   </si>
   <si>
-    <t>Create a Civilization-style grand strategy leader loading-screen character asset for the Seabird maritime intelligence platform, inspired by the provided reference screenshots but not copying any existing game character. Stylized semi-realistic 3D painterly leader, upper-body to mid-thigh crop, three-quarter pose turned slightly toward the viewer, character placed slightly right-of-center as if standing beside an information panel, hands clearly visible, diplomatic command posture, slightly enlarged expressive head and eyes, polished sculpted face, rich cloth folds, ornate costume details, metal and jewelry highlights, theatrical side key light, warm highlights with cool soft shadows, subtle rim light, crisp silhouette, premium strategy game concept art. Transparent alpha background only, no environment; if any atmosphere is needed, use only faint edge shadow on the character, not a backdrop. Leave 8-10% transparent margin around the silhouette; do not crop head, hands, or props; suitable for a React Civ-style modal character header. Output as vertical 2:3 PNG, 1024x1536, alpha channel. Character: Sukarno (수카르노). Role: 인도네시아 초대 대통령 · 독립운동 지도자 1901~1970. Type: respectful historical interpretation for a port or chokepoint region. Asset filename: region_jakarta.png. Character-specific direction: Sukarno as Indonesian independence leader; white military-style suit, black peci cap, charismatic expression; holding a proclamation folder and maritime archipelago map. Important: make the figure feel like a Civ loading-screen leader: not a normal portrait, not a photorealistic person, not a full-body fashion render. Use maritime intelligence symbols only through costume details, handheld props, badges, embroidery, documents, compasses, charts, or small artifacts.</t>
-  </si>
-  <si>
     <t>region_colombo.png</t>
   </si>
   <si>
@@ -953,9 +821,6 @@
     <t>스리랑카 폴론나루와 왕국 왕 · 1123~1186</t>
   </si>
   <si>
-    <t>Create a Civilization-style grand strategy leader loading-screen character asset for the Seabird maritime intelligence platform, inspired by the provided reference screenshots but not copying any existing game character. Stylized semi-realistic 3D painterly leader, upper-body to mid-thigh crop, three-quarter pose turned slightly toward the viewer, character placed slightly right-of-center as if standing beside an information panel, hands clearly visible, diplomatic command posture, slightly enlarged expressive head and eyes, polished sculpted face, rich cloth folds, ornate costume details, metal and jewelry highlights, theatrical side key light, warm highlights with cool soft shadows, subtle rim light, crisp silhouette, premium strategy game concept art. Transparent alpha background only, no environment; if any atmosphere is needed, use only faint edge shadow on the character, not a backdrop. Leave 8-10% transparent margin around the silhouette; do not crop head, hands, or props; suitable for a React Civ-style modal character header. Output as vertical 2:3 PNG, 1024x1536, alpha channel. Character: Parakramabahu I (파라크라마바후 1세). Role: 스리랑카 폴론나루와 왕국 왕 · 1123~1186. Type: respectful historical interpretation for a port or chokepoint region. Asset filename: region_colombo.png. Character-specific direction: Parakramabahu I as a Sri Lankan king; ancient Sinhalese royal attire with gold crown and layered ornaments; holding an irrigation-and-trade tablet and small ship charm. Important: make the figure feel like a Civ loading-screen leader: not a normal portrait, not a photorealistic person, not a full-body fashion render. Use maritime intelligence symbols only through costume details, handheld props, badges, embroidery, documents, compasses, charts, or small artifacts.</t>
-  </si>
-  <si>
     <t>region_savannah.png</t>
   </si>
   <si>
@@ -971,9 +836,6 @@
     <t>조지아 식민지 창건자 · 사바나 도시 설계 1696~1785</t>
   </si>
   <si>
-    <t>Create a Civilization-style grand strategy leader loading-screen character asset for the Seabird maritime intelligence platform, inspired by the provided reference screenshots but not copying any existing game character. Stylized semi-realistic 3D painterly leader, upper-body to mid-thigh crop, three-quarter pose turned slightly toward the viewer, character placed slightly right-of-center as if standing beside an information panel, hands clearly visible, diplomatic command posture, slightly enlarged expressive head and eyes, polished sculpted face, rich cloth folds, ornate costume details, metal and jewelry highlights, theatrical side key light, warm highlights with cool soft shadows, subtle rim light, crisp silhouette, premium strategy game concept art. Transparent alpha background only, no environment; if any atmosphere is needed, use only faint edge shadow on the character, not a backdrop. Leave 8-10% transparent margin around the silhouette; do not crop head, hands, or props; suitable for a React Civ-style modal character header. Output as vertical 2:3 PNG, 1024x1536, alpha channel. Character: James Oglethorpe (제임스 오글소프). Role: 조지아 식민지 창건자 · 사바나 도시 설계 1696~1785. Type: respectful historical interpretation for a port or chokepoint region. Asset filename: region_savannah.png. Character-specific direction: James Oglethorpe as Georgia colony founder; 18th-century British colonial officer attire, tricorn hat tucked under arm; holding a city grid plan and harbor charter. Important: make the figure feel like a Civ loading-screen leader: not a normal portrait, not a photorealistic person, not a full-body fashion render. Use maritime intelligence symbols only through costume details, handheld props, badges, embroidery, documents, compasses, charts, or small artifacts.</t>
-  </si>
-  <si>
     <t>region_hochiminhcity.png</t>
   </si>
   <si>
@@ -989,9 +851,6 @@
     <t>베트남 민주공화국 초대 주석 · 독립운동 지도자 1890~1969</t>
   </si>
   <si>
-    <t>Create a Civilization-style grand strategy leader loading-screen character asset for the Seabird maritime intelligence platform, inspired by the provided reference screenshots but not copying any existing game character. Stylized semi-realistic 3D painterly leader, upper-body to mid-thigh crop, three-quarter pose turned slightly toward the viewer, character placed slightly right-of-center as if standing beside an information panel, hands clearly visible, diplomatic command posture, slightly enlarged expressive head and eyes, polished sculpted face, rich cloth folds, ornate costume details, metal and jewelry highlights, theatrical side key light, warm highlights with cool soft shadows, subtle rim light, crisp silhouette, premium strategy game concept art. Transparent alpha background only, no environment; if any atmosphere is needed, use only faint edge shadow on the character, not a backdrop. Leave 8-10% transparent margin around the silhouette; do not crop head, hands, or props; suitable for a React Civ-style modal character header. Output as vertical 2:3 PNG, 1024x1536, alpha channel. Character: Ho Chi Minh (호찌민). Role: 베트남 민주공화국 초대 주석 · 독립운동 지도자 1890~1969. Type: respectful historical interpretation for a port or chokepoint region. Asset filename: region_hochiminhcity.png. Character-specific direction: Ho Chi Minh as Vietnamese independence leader; simple khaki tunic, light beard, gentle but firm eyes; holding a folded independence document and river-port map. Important: make the figure feel like a Civ loading-screen leader: not a normal portrait, not a photorealistic person, not a full-body fashion render. Use maritime intelligence symbols only through costume details, handheld props, badges, embroidery, documents, compasses, charts, or small artifacts.</t>
-  </si>
-  <si>
     <t>체크 항목</t>
   </si>
   <si>
@@ -1044,22 +903,173 @@
   </si>
   <si>
     <t>45개 모두 유사한 조명, 입체감, 시선, 캐릭터 크기를 유지</t>
-  </si>
-  <si>
-    <t>네거티브 프롬프트 (opaque background, white background, black background, map background, scenery, port scenery, ship scenery, UI panel, frame, border, text, captions, Korean text, logo, watermark, screenshot, full game interface, bust-only close-up, tiny full-body figure, feet-focused full body, cropped head, cropped hands, hands hidden, extra fingers, fused fingers, deformed hands, duplicated limbs, bad anatomy, distorted face, hyperrealistic photo, anime, chibi, cartoon, flat vector, low-poly, plastic toy, oil canvas texture, overpainted blur, low resolution, dull flat lighting, gore, blood, active combat, copied Civilization character)</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>네거티브 프롬프트(opaque background, white background, black background, map background, scenery, port scenery, ship scenery, UI panel, frame, border, text, captions, Korean text, logo, watermark, screenshot, full game interface, bust-only close-up, tiny full-body figure, feet-focused full body, cropped head, cropped hands, hands hidden, extra fingers, fused fingers, deformed hands, duplicated limbs, bad anatomy, distorted face, hyperrealistic photo, anime, chibi, cartoon, flat vector, low-poly, plastic toy, oil canvas texture, overpainted blur, low resolution, dull flat lighting, gore, blood, active combat, copied Civilization character)</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>스타일키워드(Civ-like loading leader, mid-thigh crop, right-side placement, stylized 3D painterly realism, ornate historical costume, hands + props visible, transparent PNG)</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>권장생성설정(1024x1536 / vertical 2:3 / PNG alpha / transparent background / 1 character only / no text / no UI / mid-thigh crop / right-of-center composition)</t>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>네거티브 프롬프트(opaque background, white background, black background, map background, scenery, port scenery, ship scenery, UI panel, frame, border, text, captions, Korean text, logo, watermark, screenshot, full game interface, bust-only close-up, tiny full-body figure, feet-focused full body, cropped head, cropped hands, hands hidden, extra fingers, fused fingers, deformed hands, duplicated limbs, bad anatomy, distorted face, hyperrealistic photo, anime, chibi, cartoon, flat vector, low-poly, plastic toy, oil canvas texture, overpainted blur, low resolution, dull flat lighting, gore, blood, active combat, copied Civilization character, 많은 장식요소-나침반, 콤파스, 조타계, 닷 등)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>네거티브 프롬프트(opaque background, white background, black background, map background, scenery, port scenery, ship scenery, UI panel, frame, border, text, captions, Korean text, logo, watermark, screenshot, full game interface, bust-only close-up, tiny full-body figure, feet-focused full body, cropped head, cropped hands, hands hidden, extra fingers, fused fingers, deformed hands, duplicated limbs, bad anatomy, distorted face, hyperrealistic photo, anime, chibi, cartoon, flat vector, low-poly, plastic toy, oil canvas texture, overpainted blur, low resolution, dull flat lighting, gore, blood, active combat, copied Civilization character, 많은 장식요소-나침반, 콤파스, 조타계, 닷 등 장식요소를 옷에 넣지 않기)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>네거티브 프롬프트(opaque background, white background, black background, map background, scenery, port scenery, ship scenery, UI panel, frame, border, text, captions, Korean text, logo, watermark, screenshot, full game interface, bust-only close-up, tiny full-body figure, feet-focused full body, cropped head, cropped hands, hands hidden, extra fingers, fused fingers, deformed hands, duplicated limbs, bad anatomy, distorted face, hyperrealistic photo, anime, chibi, cartoon, flat vector, low-poly, plastic toy, oil canvas texture, overpainted blur, low resolution, dull flat lighting, gore, blood, active combat, copied Civilization character, 의상 장식요소-나침반, 콤파스, 조타계, 닷 등 사용금지)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Create a Civilization-style grand strategy leader loading-screen character asset for the Seabird maritime intelligence platform, inspired by the provided reference screenshots but not copying any existing game character. Stylized semi-realistic 3D painterly leader, upper-body to mid-thigh crop, three-quarter pose turned slightly toward the viewer, character placed slightly right-of-center as if standing beside an information panel, hands clearly visible, diplomatic command posture, slightly enlarged expressive head and eyes, polished sculpted face, heatrical side key light, warm highlights with cool soft shadows, subtle rim light, crisp silhouette, premium strategy game concept art. Transparent alpha background only, no environment; if any atmosphere is needed, use only faint edge shadow on the character, not a backdrop. Leave 8-10% transparent margin around the silhouette; do not crop head, hands, or props; suitable for a React Civ-style modal character header. Output as vertical 2:3 PNG, 1024x1536, alpha channel. Character: Park Seo-yeon (박서연). Role: 글로벌 컨테이너 선단 선장. Type: fictional modern maritime archetype. Asset filename: ship_container.png. Character-specific direction: Korean woman in her early 40s, global container fleet captain; crisp white naval captain uniform with gold epaulettes and four sleeve stripes; short black hair, calm strategic gaze; hands clasped around a small brass compass and folded global route chart; subtle container-stack motif embroidered on cuffs. Important: make the figure feel like a Civ loading-screen leader: not a normal portrait, not a photorealistic person, not a full-body fashion render. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Create a Civilization-style grand strategy leader loading-screen character asset for the Seabird maritime intelligence platform, inspired by the provided reference screenshots but not copying any existing game character. Stylized semi-realistic 3D painterly leader, upper-body to mid-thigh crop, three-quarter pose turned slightly toward the viewer, character placed slightly right-of-center as if standing beside an information panel, hands clearly visible, diplomatic command posture, slightly enlarged expressive head and eyes, polished sculpted face, heatrical side key light, warm highlights with cool soft shadows, subtle rim light, crisp silhouette, premium strategy game concept art. Transparent alpha background only, no environment; if any atmosphere is needed, use only faint edge shadow on the character, not a backdrop. Leave 8-10% transparent margin around the silhouette; do not crop head, hands, or props; suitable for a React Civ-style modal character header. Output as vertical 2:3 PNG, 1024x1536, alpha channel. Character: Karim Al-Rashid (카림 알-라시드). Role: 원유 탱커 수석 엔지니어. Type: fictional modern maritime archetype. Asset filename: ship_tanker.png. Character-specific direction: Arab man in his late 40s, oil tanker chief engineer; navy coveralls upgraded into a ceremonial engineer coat with orange safety piping and brass pressure-gauge badges; short gray-flecked beard; one hand holds an oil-route clipboard, the other rests near a brass valve wheel prop. Important: make the figure feel like a Civ loading-screen leader: not a normal portrait, not a photorealistic person, not a full-body fashion render. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Create a Civilization-style grand strategy leader loading-screen character asset for the Seabird maritime intelligence platform, inspired by the provided reference screenshots but not copying any existing game character. Stylized semi-realistic 3D painterly leader, upper-body to mid-thigh crop, three-quarter pose turned slightly toward the viewer, character placed slightly right-of-center as if standing beside an information panel, hands clearly visible, diplomatic command posture, slightly enlarged expressive head and eyes, polished sculpted face, heatrical side key light, warm highlights with cool soft shadows, subtle rim light, crisp silhouette, premium strategy game concept art. Transparent alpha background only, no environment; if any atmosphere is needed, use only faint edge shadow on the character, not a backdrop. Leave 8-10% transparent margin around the silhouette; do not crop head, hands, or props; suitable for a React Civ-style modal character header. Output as vertical 2:3 PNG, 1024x1536, alpha channel. Character: Amadou Diallo (아마두 디알로). Role: 벌크선 화물장. Type: fictional modern maritime archetype. Asset filename: ship_bulk.png. Character-specific direction: West African man in his 50s, bulk carrier cargo master; heavy navy work jacket with ochre mineral-dust weathering and gold-edged rank patches; powerful hands holding a miniature ore sample and cargo manifest; wise, steady expression. Important: make the figure feel like a Civ loading-screen leader: not a normal portrait, not a photorealistic person, not a full-body fashion render. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Create a Civilization-style grand strategy leader loading-screen character asset for the Seabird maritime intelligence platform, inspired by the provided reference screenshots but not copying any existing game character. Stylized semi-realistic 3D painterly leader, upper-body to mid-thigh crop, three-quarter pose turned slightly toward the viewer, character placed slightly right-of-center as if standing beside an information panel, hands clearly visible, diplomatic command posture, slightly enlarged expressive head and eyes, polished sculpted face, heatrical side key light, warm highlights with cool soft shadows, subtle rim light, crisp silhouette, premium strategy game concept art. Transparent alpha background only, no environment; if any atmosphere is needed, use only faint edge shadow on the character, not a backdrop. Leave 8-10% transparent margin around the silhouette; do not crop head, hands, or props; suitable for a React Civ-style modal character header. Output as vertical 2:3 PNG, 1024x1536, alpha channel. Character: Sofia Berg (소피아 베르그). Role: LNG 안전관제 책임자. Type: fictional modern maritime archetype. Asset filename: ship_lng.png. Character-specific direction: Scandinavian woman in her mid-30s, LNG safety-control officer; orange fire-retardant uniform shaped like a formal leader coat, white safety helmet tucked under one arm; icy-blue trim, sensor badge, analytical eyes; holding a cryogenic safety tablet. Important: make the figure feel like a Civ loading-screen leader: not a normal portrait, not a photorealistic person, not a full-body fashion render. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Create a Civilization-style grand strategy leader loading-screen character asset for the Seabird maritime intelligence platform, inspired by the provided reference screenshots but not copying any existing game character. Stylized semi-realistic 3D painterly leader, upper-body to mid-thigh crop, three-quarter pose turned slightly toward the viewer, character placed slightly right-of-center as if standing beside an information panel, hands clearly visible, diplomatic command posture, slightly enlarged expressive head and eyes, polished sculpted face, heatrical side key light, warm highlights with cool soft shadows, subtle rim light, crisp silhouette, premium strategy game concept art. Transparent alpha background only, no environment; if any atmosphere is needed, use only faint edge shadow on the character, not a backdrop. Leave 8-10% transparent margin around the silhouette; do not crop head, hands, or props; suitable for a React Civ-style modal character header. Output as vertical 2:3 PNG, 1024x1536, alpha channel. Character: Arjun Mehta (아르준 메타). Role: 크루즈 선장. Type: fictional modern maritime archetype. Asset filename: ship_passenger.png. Character-specific direction: Indian man in his 50s, luxury cruise captain; pristine white dress uniform with four gold stripes, medal ribbons, deep blue sash; salt-and-pepper hair and mustache; one hand holds a folded passenger manifest, the other rests confidently at the waist. Important: make the figure feel like a Civ loading-screen leader: not a normal portrait, not a photorealistic person, not a full-body fashion render. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Create a Civilization-style grand strategy leader loading-screen character asset for the Seabird maritime intelligence platform, inspired by the provided reference screenshots but not copying any existing game character. Stylized semi-realistic 3D painterly leader, upper-body to mid-thigh crop, three-quarter pose turned slightly toward the viewer, character placed slightly right-of-center as if standing beside an information panel, hands clearly visible, diplomatic command posture, slightly enlarged expressive head and eyes, polished sculpted face, heatrical side key light, warm highlights with cool soft shadows, subtle rim light, crisp silhouette, premium strategy game concept art. Transparent alpha background only, no environment; if any atmosphere is needed, use only faint edge shadow on the character, not a backdrop. Leave 8-10% transparent margin around the silhouette; do not crop head, hands, or props; suitable for a React Civ-style modal character header. Output as vertical 2:3 PNG, 1024x1536, alpha channel. Character: Maria Santos (마리아 산토스). Role: 원양어선 선장. Type: fictional modern maritime archetype. Asset filename: ship_fishing.png. Character-specific direction: Filipino woman in her 40s, deep-sea fishing captain; weathered orange rain slicker reinterpreted as a dignified sea-leader coat, rubberized cuffs, net-knot brooch; gray-streaked hair tied back; holding a coiled fishing line and small sonar screen. Important: make the figure feel like a Civ loading-screen leader: not a normal portrait, not a photorealistic person, not a full-body fashion render. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Create a Civilization-style grand strategy leader loading-screen character asset for the Seabird maritime intelligence platform, inspired by the provided reference screenshots but not copying any existing game character. Stylized semi-realistic 3D painterly leader, upper-body to mid-thigh crop, three-quarter pose turned slightly toward the viewer, character placed slightly right-of-center as if standing beside an information panel, hands clearly visible, diplomatic command posture, slightly enlarged expressive head and eyes, polished sculpted face, heatrical side key light, warm highlights with cool soft shadows, subtle rim light, crisp silhouette, premium strategy game concept art. Transparent alpha background only, no environment; if any atmosphere is needed, use only faint edge shadow on the character, not a backdrop. Leave 8-10% transparent margin around the silhouette; do not crop head, hands, or props; suitable for a React Civ-style modal character header. Output as vertical 2:3 PNG, 1024x1536, alpha channel. Character: Juan Carrera (후안 카레라). Role: 해양 구조·특수 작전 지휘관. Type: fictional modern maritime archetype. Asset filename: ship_special.png. Character-specific direction: Latin American man in his 40s, naval rescue and special-operations commander; dark navy tactical uniform with rescue insignia, orange rescue cord, compact radio on chest; intense focused expression; one hand holds a signal flare case, the other a waterproof mission map. Important: make the figure feel like a Civ loading-screen leader: not a normal portrait, not a photorealistic person, not a full-body fashion render. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Create a Civilization-style grand strategy leader loading-screen character asset for the Seabird maritime intelligence platform, inspired by the provided reference screenshots but not copying any existing game character. Stylized semi-realistic 3D painterly leader, upper-body to mid-thigh crop, three-quarter pose turned slightly toward the viewer, character placed slightly right-of-center as if standing beside an information panel, hands clearly visible, diplomatic command posture, slightly enlarged expressive head and eyes, polished sculpted face, heatrical side key light, warm highlights with cool soft shadows, subtle rim light, crisp silhouette, premium strategy game concept art. Transparent alpha background only, no environment; if any atmosphere is needed, use only faint edge shadow on the character, not a backdrop. Leave 8-10% transparent margin around the silhouette; do not crop head, hands, or props; suitable for a React Civ-style modal character header. Output as vertical 2:3 PNG, 1024x1536, alpha channel. Character: Aina Åberg (아이나 오베르그). Role: 미지 항로 항법사. Type: fictional modern maritime archetype. Asset filename: ship_other.png. Character-specific direction: Sámi-Scandinavian woman in her 30s, navigator of unknown routes; dark teal explorer coat with Sámi-inspired geometric trim, silver compass pendant, pale braided hair; holding an antique astrolabe and a glowing unknown sea-route note. Important: make the figure feel like a Civ loading-screen leader: not a normal portrait, not a photorealistic person, not a full-body fashion render. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Create a Civilization-style grand strategy leader loading-screen character asset for the Seabird maritime intelligence platform, inspired by the provided reference screenshots but not copying any existing game character. Stylized semi-realistic 3D painterly leader, upper-body to mid-thigh crop, three-quarter pose turned slightly toward the viewer, character placed slightly right-of-center as if standing beside an information panel, hands clearly visible, diplomatic command posture, slightly enlarged expressive head and eyes, polished sculpted face, heatrical side key light, warm highlights with cool soft shadows, subtle rim light, crisp silhouette, premium strategy game concept art. Transparent alpha background only, no environment; if any atmosphere is needed, use only faint edge shadow on the character, not a backdrop. Leave 8-10% transparent margin around the silhouette; do not crop head, hands, or props; suitable for a React Civ-style modal character header. Output as vertical 2:3 PNG, 1024x1536, alpha channel. Character: Gamal Abdel Nasser (가말 압델 나세르). Role: 이집트 제2대 대통령 · 수에즈 국유화 1956. Type: respectful historical interpretation for a port or chokepoint region. Asset filename: region_suez.png. Character-specific direction: Gamal Abdel Nasser as a charismatic 1950s Egyptian statesman; khaki military dress uniform with restrained medals, strong brows, confident posture; holding a rolled Suez Canal treaty and brass canal ruler; subtle Egyptian eagle pin. Important: make the figure feel like a Civ loading-screen leader: not a normal portrait, not a photorealistic person, not a full-body fashion render. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Create a Civilization-style grand strategy leader loading-screen character asset for the Seabird maritime intelligence platform, inspired by the provided reference screenshots but not copying any existing game character. Stylized semi-realistic 3D painterly leader, upper-body to mid-thigh crop, three-quarter pose turned slightly toward the viewer, character placed slightly right-of-center as if standing beside an information panel, hands clearly visible, diplomatic command posture, slightly enlarged expressive head and eyes, polished sculpted face, heatrical side key light, warm highlights with cool soft shadows, subtle rim light, crisp silhouette, premium strategy game concept art. Transparent alpha background only, no environment; if any atmosphere is needed, use only faint edge shadow on the character, not a backdrop. Leave 8-10% transparent margin around the silhouette; do not crop head, hands, or props; suitable for a React Civ-style modal character header. Output as vertical 2:3 PNG, 1024x1536, alpha channel. Character: Hang Tuah (항 투아). Role: 말라카 전설의 제독 · 15세기. Type: respectful historical interpretation for a port or chokepoint region. Asset filename: region_malacca.png. Character-specific direction: Hang Tuah as a legendary Malay admiral; ornate 15th-century Malay warrior attire with gold-thread songket, keris at the belt, wrapped headcloth; one hand near the keris hilt, the other holding a strait navigation scroll; loyal fierce gaze. Important: make the figure feel like a Civ loading-screen leader: not a normal portrait, not a photorealistic person, not a full-body fashion render. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Create a Civilization-style grand strategy leader loading-screen character asset for the Seabird maritime intelligence platform, inspired by the provided reference screenshots but not copying any existing game character. Stylized semi-realistic 3D painterly leader, upper-body to mid-thigh crop, three-quarter pose turned slightly toward the viewer, character placed slightly right-of-center as if standing beside an information panel, hands clearly visible, diplomatic command posture, slightly enlarged expressive head and eyes, polished sculpted face, heatrical side key light, warm highlights with cool soft shadows, subtle rim light, crisp silhouette, premium strategy game concept art. Transparent alpha background only, no environment; if any atmosphere is needed, use only faint edge shadow on the character, not a backdrop. Leave 8-10% transparent margin around the silhouette; do not crop head, hands, or props; suitable for a React Civ-style modal character header. Output as vertical 2:3 PNG, 1024x1536, alpha channel. Character: Darius the Great (다리우스 대왕). Role: 페르시아 아케메네스 제국 3대 왕 · 기원전 550~486. Type: respectful historical interpretation for a port or chokepoint region. Asset filename: region_hormuz.png. Character-specific direction: Darius the Great as an Achaemenid Persian king; elaborate patterned royal robe, tall Persian crown, curled beard with gold ornaments; holding a carved tablet of tribute routes and a small Gulf trade seal; imperial, measured expression. Important: make the figure feel like a Civ loading-screen leader: not a normal portrait, not a photorealistic person, not a full-body fashion render. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Create a Civilization-style grand strategy leader loading-screen character asset for the Seabird maritime intelligence platform, inspired by the provided reference screenshots but not copying any existing game character. Stylized semi-realistic 3D painterly leader, upper-body to mid-thigh crop, three-quarter pose turned slightly toward the viewer, character placed slightly right-of-center as if standing beside an information panel, hands clearly visible, diplomatic command posture, slightly enlarged expressive head and eyes, polished sculpted face, heatrical side key light, warm highlights with cool soft shadows, subtle rim light, crisp silhouette, premium strategy game concept art. Transparent alpha background only, no environment; if any atmosphere is needed, use only faint edge shadow on the character, not a backdrop. Leave 8-10% transparent margin around the silhouette; do not crop head, hands, or props; suitable for a React Civ-style modal character header. Output as vertical 2:3 PNG, 1024x1536, alpha channel. Character: Omar Torrijos (오마르 토리호스). Role: 파나마 최고지도자 · 운하 반환 협상가 1968~1981. Type: respectful historical interpretation for a port or chokepoint region. Asset filename: region_panama.png. Character-specific direction: Omar Torrijos as a 1970s Panamanian military leader; olive-green uniform with general insignia, rolled sleeves, populist direct gaze; holding a Panama Canal transfer document and canal-lock schematic. Important: make the figure feel like a Civ loading-screen leader: not a normal portrait, not a photorealistic person, not a full-body fashion render. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Create a Civilization-style grand strategy leader loading-screen character asset for the Seabird maritime intelligence platform, inspired by the provided reference screenshots but not copying any existing game character. Stylized semi-realistic 3D painterly leader, upper-body to mid-thigh crop, three-quarter pose turned slightly toward the viewer, character placed slightly right-of-center as if standing beside an information panel, hands clearly visible, diplomatic command posture, slightly enlarged expressive head and eyes, polished sculpted face, heatrical side key light, warm highlights with cool soft shadows, subtle rim light, crisp silhouette, premium strategy game concept art. Transparent alpha background only, no environment; if any atmosphere is needed, use only faint edge shadow on the character, not a backdrop. Leave 8-10% transparent margin around the silhouette; do not crop head, hands, or props; suitable for a React Civ-style modal character header. Output as vertical 2:3 PNG, 1024x1536, alpha channel. Character: Admiral Horatio Nelson (호레이쇼 넬슨 제독). Role: 영국 해군 원수 · 트라팔가르 해전 영웅 1805. Type: respectful historical interpretation for a port or chokepoint region. Asset filename: region_dover.png. Character-specific direction: Admiral Horatio Nelson as a British naval hero; early-1800s Royal Navy dress uniform with gold epaulettes, decorations, empty sleeve detail; telescope under one arm, hand over naval chart; resolute expression. Important: make the figure feel like a Civ loading-screen leader: not a normal portrait, not a photorealistic person, not a full-body fashion render. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Create a Civilization-style grand strategy leader loading-screen character asset for the Seabird maritime intelligence platform, inspired by the provided reference screenshots but not copying any existing game character. Stylized semi-realistic 3D painterly leader, upper-body to mid-thigh crop, three-quarter pose turned slightly toward the viewer, character placed slightly right-of-center as if standing beside an information panel, hands clearly visible, diplomatic command posture, slightly enlarged expressive head and eyes, polished sculpted face, heatrical side key light, warm highlights with cool soft shadows, subtle rim light, crisp silhouette, premium strategy game concept art. Transparent alpha background only, no environment; if any atmosphere is needed, use only faint edge shadow on the character, not a backdrop. Leave 8-10% transparent margin around the silhouette; do not crop head, hands, or props; suitable for a React Civ-style modal character header. Output as vertical 2:3 PNG, 1024x1536, alpha channel. Character: Yi Sun-sin (이순신). Role: 조선 삼도수군통제사 · 1545~1598. Type: respectful historical interpretation for a port or chokepoint region. Asset filename: region_korea_strait.png. Character-specific direction: Yi Sun-sin as a Joseon admiral; ornate Korean commander armor and red command robe, winged helmet, calm uncompromising expression; holding a command baton and compact turtle-ship route map. Important: make the figure feel like a Civ loading-screen leader: not a normal portrait, not a photorealistic person, not a full-body fashion render. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Create a Civilization-style grand strategy leader loading-screen character asset for the Seabird maritime intelligence platform, inspired by the provided reference screenshots but not copying any existing game character. Stylized semi-realistic 3D painterly leader, upper-body to mid-thigh crop, three-quarter pose turned slightly toward the viewer, character placed slightly right-of-center as if standing beside an information panel, hands clearly visible, diplomatic command posture, slightly enlarged expressive head and eyes, polished sculpted face, heatrical side key light, warm highlights with cool soft shadows, subtle rim light, crisp silhouette, premium strategy game concept art. Transparent alpha background only, no environment; if any atmosphere is needed, use only faint edge shadow on the character, not a backdrop. Leave 8-10% transparent margin around the silhouette; do not crop head, hands, or props; suitable for a React Civ-style modal character header. Output as vertical 2:3 PNG, 1024x1536, alpha channel. Character: Queen of Sheba (시바의 여왕). Role: 예멘·에티오피아의 전설적 여왕 · 기원전 10세기. Type: respectful historical interpretation for a port or chokepoint region. Asset filename: region_bab_el_mandeb.png. Character-specific direction: Queen of Sheba as a legendary Sabaean/Ethiopian maritime-trade queen; ancient royal attire with gold jewelry, layered textiles, sculptural headdress; dark skin, mysterious authority; holding incense resin and a Red Sea trade tablet. Important: make the figure feel like a Civ loading-screen leader: not a normal portrait, not a photorealistic person, not a full-body fashion render. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Create a Civilization-style grand strategy leader loading-screen character asset for the Seabird maritime intelligence platform, inspired by the provided reference screenshots but not copying any existing game character. Stylized semi-realistic 3D painterly leader, upper-body to mid-thigh crop, three-quarter pose turned slightly toward the viewer, character placed slightly right-of-center as if standing beside an information panel, hands clearly visible, diplomatic command posture, slightly enlarged expressive head and eyes, polished sculpted face, heatrical side key light, warm highlights with cool soft shadows, subtle rim light, crisp silhouette, premium strategy game concept art. Transparent alpha background only, no environment; if any atmosphere is needed, use only faint edge shadow on the character, not a backdrop. Leave 8-10% transparent margin around the silhouette; do not crop head, hands, or props; suitable for a React Civ-style modal character header. Output as vertical 2:3 PNG, 1024x1536, alpha channel. Character: Jang Bogo (장보고). Role: 신라 해상왕 · 9세기 동아시아 무역 제패. Type: respectful historical interpretation for a port or chokepoint region. Asset filename: region_busan.png. Character-specific direction: Jang Bogo as a Silla maritime trade commander; 9th-century Korean military-trade robes with armor panels, sea-green sash, merchant-seal pendant; holding a folded East Asia trade-route scroll. Important: make the figure feel like a Civ loading-screen leader: not a normal portrait, not a photorealistic person, not a full-body fashion render. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Create a Civilization-style grand strategy leader loading-screen character asset for the Seabird maritime intelligence platform, inspired by the provided reference screenshots but not copying any existing game character. Stylized semi-realistic 3D painterly leader, upper-body to mid-thigh crop, three-quarter pose turned slightly toward the viewer, character placed slightly right-of-center as if standing beside an information panel, hands clearly visible, diplomatic command posture, slightly enlarged expressive head and eyes, polished sculpted face, heatrical side key light, warm highlights with cool soft shadows, subtle rim light, crisp silhouette, premium strategy game concept art. Transparent alpha background only, no environment; if any atmosphere is needed, use only faint edge shadow on the character, not a backdrop. Leave 8-10% transparent margin around the silhouette; do not crop head, hands, or props; suitable for a React Civ-style modal character header. Output as vertical 2:3 PNG, 1024x1536, alpha channel. Character: Gang Gam-chan (강감찬). Role: 고려 명장 · 귀주대첩으로 거란 격퇴 1019. Type: respectful historical interpretation for a port or chokepoint region. Asset filename: region_incheon.png. Character-specific direction: Gang Gam-chan as a Goryeo strategist; formal Goryeo court armor and scholar-general robe, gray beard, disciplined gaze; hands clasped over a defensive map tablet and command tally. Important: make the figure feel like a Civ loading-screen leader: not a normal portrait, not a photorealistic person, not a full-body fashion render. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Create a Civilization-style grand strategy leader loading-screen character asset for the Seabird maritime intelligence platform, inspired by the provided reference screenshots but not copying any existing game character. Stylized semi-realistic 3D painterly leader, upper-body to mid-thigh crop, three-quarter pose turned slightly toward the viewer, character placed slightly right-of-center as if standing beside an information panel, hands clearly visible, diplomatic command posture, slightly enlarged expressive head and eyes, polished sculpted face, heatrical side key light, warm highlights with cool soft shadows, subtle rim light, crisp silhouette, premium strategy game concept art. Transparent alpha background only, no environment; if any atmosphere is needed, use only faint edge shadow on the character, not a backdrop. Leave 8-10% transparent margin around the silhouette; do not crop head, hands, or props; suitable for a React Civ-style modal character header. Output as vertical 2:3 PNG, 1024x1536, alpha channel. Character: Park Tae-joon (박태준). Role: 포스코 설립자 · 한국 철강산업의 아버지. Type: respectful historical interpretation for a port or chokepoint region. Asset filename: region_gwangyang.png. Character-specific direction: Park Tae-joon as a modern industrial founder; dignified 1970s Korean business suit subtly armored with steel-blue lapel shine; holding a steel ingot sample and port-industrial blueprint; visionary but austere. Important: make the figure feel like a Civ loading-screen leader: not a normal portrait, not a photorealistic person, not a full-body fashion render. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Create a Civilization-style grand strategy leader loading-screen character asset for the Seabird maritime intelligence platform, inspired by the provided reference screenshots but not copying any existing game character. Stylized semi-realistic 3D painterly leader, upper-body to mid-thigh crop, three-quarter pose turned slightly toward the viewer, character placed slightly right-of-center as if standing beside an information panel, hands clearly visible, diplomatic command posture, slightly enlarged expressive head and eyes, polished sculpted face, heatrical side key light, warm highlights with cool soft shadows, subtle rim light, crisp silhouette, premium strategy game concept art. Transparent alpha background only, no environment; if any atmosphere is needed, use only faint edge shadow on the character, not a backdrop. Leave 8-10% transparent margin around the silhouette; do not crop head, hands, or props; suitable for a React Civ-style modal character header. Output as vertical 2:3 PNG, 1024x1536, alpha channel. Character: Lee Kuan Yew (리콴유). Role: 싱가포르 초대 총리 · 건국의 아버지 1959~1990. Type: respectful historical interpretation for a port or chokepoint region. Asset filename: region_singapore.png. Character-specific direction: Lee Kuan Yew as a statesman of modern Singapore; immaculate white short-sleeve formal shirt with dark trousers, understated pen and papers; holding a port-city masterplan folder; sharp pragmatic gaze. Important: make the figure feel like a Civ loading-screen leader: not a normal portrait, not a photorealistic person, not a full-body fashion render. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Create a Civilization-style grand strategy leader loading-screen character asset for the Seabird maritime intelligence platform, inspired by the provided reference screenshots but not copying any existing game character. Stylized semi-realistic 3D painterly leader, upper-body to mid-thigh crop, three-quarter pose turned slightly toward the viewer, character placed slightly right-of-center as if standing beside an information panel, hands clearly visible, diplomatic command posture, slightly enlarged expressive head and eyes, polished sculpted face, heatrical side key light, warm highlights with cool soft shadows, subtle rim light, crisp silhouette, premium strategy game concept art. Transparent alpha background only, no environment; if any atmosphere is needed, use only faint edge shadow on the character, not a backdrop. Leave 8-10% transparent margin around the silhouette; do not crop head, hands, or props; suitable for a React Civ-style modal character header. Output as vertical 2:3 PNG, 1024x1536, alpha channel. Character: Zheng He (정화). Role: 명나라 대항해사 · 1405~1433년 7차 대원정. Type: respectful historical interpretation for a port or chokepoint region. Asset filename: region_shanghai.png. Character-specific direction: Zheng He as a Ming dynasty grand admiral; richly embroidered red-and-gold admiral robe, court hat, powerful seafarer presence; holding a treasure-fleet scroll and nautical compass. Important: make the figure feel like a Civ loading-screen leader: not a normal portrait, not a photorealistic person, not a full-body fashion render. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Create a Civilization-style grand strategy leader loading-screen character asset for the Seabird maritime intelligence platform, inspired by the provided reference screenshots but not copying any existing game character. Stylized semi-realistic 3D painterly leader, upper-body to mid-thigh crop, three-quarter pose turned slightly toward the viewer, character placed slightly right-of-center as if standing beside an information panel, hands clearly visible, diplomatic command posture, slightly enlarged expressive head and eyes, polished sculpted face, heatrical side key light, warm highlights with cool soft shadows, subtle rim light, crisp silhouette, premium strategy game concept art. Transparent alpha background only, no environment; if any atmosphere is needed, use only faint edge shadow on the character, not a backdrop. Leave 8-10% transparent margin around the silhouette; do not crop head, hands, or props; suitable for a React Civ-style modal character header. Output as vertical 2:3 PNG, 1024x1536, alpha channel. Character: Desiderius Erasmus (에라스무스). Role: 로테르담 출신 인문학자 · 1469~1536. Type: respectful historical interpretation for a port or chokepoint region. Asset filename: region_rotterdam.png. Character-specific direction: Desiderius Erasmus as a Renaissance humanist from Rotterdam; scholar robes with fur trim, soft cap, thoughtful eyes; holding an open book and a tiny brass ship token marking humanist trade routes. Important: make the figure feel like a Civ loading-screen leader: not a normal portrait, not a photorealistic person, not a full-body fashion render. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Create a Civilization-style grand strategy leader loading-screen character asset for the Seabird maritime intelligence platform, inspired by the provided reference screenshots but not copying any existing game character. Stylized semi-realistic 3D painterly leader, upper-body to mid-thigh crop, three-quarter pose turned slightly toward the viewer, character placed slightly right-of-center as if standing beside an information panel, hands clearly visible, diplomatic command posture, slightly enlarged expressive head and eyes, polished sculpted face, heatrical side key light, warm highlights with cool soft shadows, subtle rim light, crisp silhouette, premium strategy game concept art. Transparent alpha background only, no environment; if any atmosphere is needed, use only faint edge shadow on the character, not a backdrop. Leave 8-10% transparent margin around the silhouette; do not crop head, hands, or props; suitable for a React Civ-style modal character header. Output as vertical 2:3 PNG, 1024x1536, alpha channel. Character: Commodore Matthew Perry (매슈 페리 제독). Role: 미 해군 제독 · 태평양 무역로 개척 1853. Type: respectful historical interpretation for a port or chokepoint region. Asset filename: region_la_lb.png. Character-specific direction: Commodore Matthew Perry as a 19th-century U.S. naval officer; dark navy commodore uniform with epaulettes, stern diplomatic expression; holding a naval dispatch and spyglass; maritime trade envoy mood. Important: make the figure feel like a Civ loading-screen leader: not a normal portrait, not a photorealistic person, not a full-body fashion render. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Create a Civilization-style grand strategy leader loading-screen character asset for the Seabird maritime intelligence platform, inspired by the provided reference screenshots but not copying any existing game character. Stylized semi-realistic 3D painterly leader, upper-body to mid-thigh crop, three-quarter pose turned slightly toward the viewer, character placed slightly right-of-center as if standing beside an information panel, hands clearly visible, diplomatic command posture, slightly enlarged expressive head and eyes, polished sculpted face, heatrical side key light, warm highlights with cool soft shadows, subtle rim light, crisp silhouette, premium strategy game concept art. Transparent alpha background only, no environment; if any atmosphere is needed, use only faint edge shadow on the character, not a backdrop. Leave 8-10% transparent margin around the silhouette; do not crop head, hands, or props; suitable for a React Civ-style modal character header. Output as vertical 2:3 PNG, 1024x1536, alpha channel. Character: Sheikh Rashid bin Saeed Al Maktoum (라시드 빈 사이드). Role: 두바이 근대화의 아버지 · 재위 1958~1990. Type: respectful historical interpretation for a port or chokepoint region. Asset filename: region_dubai.png. Character-specific direction: Sheikh Rashid bin Saeed Al Maktoum as Dubai's modernization ruler; white kandura, bisht with gold trim, ghutra and agal; holding a harbor development plan and pearl-trade token; warm visionary authority. Important: make the figure feel like a Civ loading-screen leader: not a normal portrait, not a photorealistic person, not a full-body fashion render. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Create a Civilization-style grand strategy leader loading-screen character asset for the Seabird maritime intelligence platform, inspired by the provided reference screenshots but not copying any existing game character. Stylized semi-realistic 3D painterly leader, upper-body to mid-thigh crop, three-quarter pose turned slightly toward the viewer, character placed slightly right-of-center as if standing beside an information panel, hands clearly visible, diplomatic command posture, slightly enlarged expressive head and eyes, polished sculpted face, heatrical side key light, warm highlights with cool soft shadows, subtle rim light, crisp silhouette, premium strategy game concept art. Transparent alpha background only, no environment; if any atmosphere is needed, use only faint edge shadow on the character, not a backdrop. Leave 8-10% transparent margin around the silhouette; do not crop head, hands, or props; suitable for a React Civ-style modal character header. Output as vertical 2:3 PNG, 1024x1536, alpha channel. Character: Sakamoto Ryoma (사카모토 료마). Role: 막말 지사 · 일본 개국·근대화 선구자 1836~1867. Type: respectful historical interpretation for a port or chokepoint region. Asset filename: region_yokohama.png. Character-specific direction: Sakamoto Ryoma as a Bakumatsu reformer; kimono and haori mixed with early modern maritime elements, sword at side but non-combat pose; holding a trade agreement scroll and compass. Important: make the figure feel like a Civ loading-screen leader: not a normal portrait, not a photorealistic person, not a full-body fashion render. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Create a Civilization-style grand strategy leader loading-screen character asset for the Seabird maritime intelligence platform, inspired by the provided reference screenshots but not copying any existing game character. Stylized semi-realistic 3D painterly leader, upper-body to mid-thigh crop, three-quarter pose turned slightly toward the viewer, character placed slightly right-of-center as if standing beside an information panel, hands clearly visible, diplomatic command posture, slightly enlarged expressive head and eyes, polished sculpted face, heatrical side key light, warm highlights with cool soft shadows, subtle rim light, crisp silhouette, premium strategy game concept art. Transparent alpha background only, no environment; if any atmosphere is needed, use only faint edge shadow on the character, not a backdrop. Leave 8-10% transparent margin around the silhouette; do not crop head, hands, or props; suitable for a React Civ-style modal character header. Output as vertical 2:3 PNG, 1024x1536, alpha channel. Character: Taira no Kiyomori (타이라노 키요모리). Role: 헤이안 말기 무장 · 효고 항구 개발자 1118~1181. Type: respectful historical interpretation for a port or chokepoint region. Asset filename: region_kobe.png. Character-specific direction: Taira no Kiyomori as a late-Heian warrior leader; ornate samurai court armor with crimson silk layers and formal eboshi; holding a port charter scroll; commanding noble gaze. Important: make the figure feel like a Civ loading-screen leader: not a normal portrait, not a photorealistic person, not a full-body fashion render. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Create a Civilization-style grand strategy leader loading-screen character asset for the Seabird maritime intelligence platform, inspired by the provided reference screenshots but not copying any existing game character. Stylized semi-realistic 3D painterly leader, upper-body to mid-thigh crop, three-quarter pose turned slightly toward the viewer, character placed slightly right-of-center as if standing beside an information panel, hands clearly visible, diplomatic command posture, slightly enlarged expressive head and eyes, polished sculpted face, heatrical side key light, warm highlights with cool soft shadows, subtle rim light, crisp silhouette, premium strategy game concept art. Transparent alpha background only, no environment; if any atmosphere is needed, use only faint edge shadow on the character, not a backdrop. Leave 8-10% transparent margin around the silhouette; do not crop head, hands, or props; suitable for a React Civ-style modal character header. Output as vertical 2:3 PNG, 1024x1536, alpha channel. Character: Wang Zhi (왕직). Role: 명나라 해상 무역상 · 동아시아 밀무역의 왕 ?~1559. Type: respectful historical interpretation for a port or chokepoint region. Asset filename: region_ningbo.png. Character-specific direction: Wang Zhi as a Ming-era maritime trader; layered merchant-warrior robes, discreet armor plates, confident ambiguous smile; holding a ledger, seal, and rolled coastal trade map. Important: make the figure feel like a Civ loading-screen leader: not a normal portrait, not a photorealistic person, not a full-body fashion render. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Create a Civilization-style grand strategy leader loading-screen character asset for the Seabird maritime intelligence platform, inspired by the provided reference screenshots but not copying any existing game character. Stylized semi-realistic 3D painterly leader, upper-body to mid-thigh crop, three-quarter pose turned slightly toward the viewer, character placed slightly right-of-center as if standing beside an information panel, hands clearly visible, diplomatic command posture, slightly enlarged expressive head and eyes, polished sculpted face, heatrical side key light, warm highlights with cool soft shadows, subtle rim light, crisp silhouette, premium strategy game concept art. Transparent alpha background only, no environment; if any atmosphere is needed, use only faint edge shadow on the character, not a backdrop. Leave 8-10% transparent margin around the silhouette; do not crop head, hands, or props; suitable for a React Civ-style modal character header. Output as vertical 2:3 PNG, 1024x1536, alpha channel. Character: Deng Xiaoping (덩샤오핑). Role: 중국 최고 지도자 · 개혁개방·선전 경제특구 창설 1904~1997. Type: respectful historical interpretation for a port or chokepoint region. Asset filename: region_shenzhen.png. Character-specific direction: Deng Xiaoping as a reform-era Chinese leader; simple gray Zhongshan suit, elder strategist posture; holding a special economic zone blueprint and small abacus; pragmatic gaze. Important: make the figure feel like a Civ loading-screen leader: not a normal portrait, not a photorealistic person, not a full-body fashion render. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Create a Civilization-style grand strategy leader loading-screen character asset for the Seabird maritime intelligence platform, inspired by the provided reference screenshots but not copying any existing game character. Stylized semi-realistic 3D painterly leader, upper-body to mid-thigh crop, three-quarter pose turned slightly toward the viewer, character placed slightly right-of-center as if standing beside an information panel, hands clearly visible, diplomatic command posture, slightly enlarged expressive head and eyes, polished sculpted face, heatrical side key light, warm highlights with cool soft shadows, subtle rim light, crisp silhouette, premium strategy game concept art. Transparent alpha background only, no environment; if any atmosphere is needed, use only faint edge shadow on the character, not a backdrop. Leave 8-10% transparent margin around the silhouette; do not crop head, hands, or props; suitable for a React Civ-style modal character header. Output as vertical 2:3 PNG, 1024x1536, alpha channel. Character: Lin Zexu (린쩌쉬). Role: 청나라 흠차대신 · 아편전쟁 저항의 영웅 1785~1850. Type: respectful historical interpretation for a port or chokepoint region. Asset filename: region_hongkong.png. Character-specific direction: Lin Zexu as a Qing commissioner; formal Qing official robe with rank badge, mandarin hat, stern moral expression; holding an imperial edict and port-control ledger. Important: make the figure feel like a Civ loading-screen leader: not a normal portrait, not a photorealistic person, not a full-body fashion render. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Create a Civilization-style grand strategy leader loading-screen character asset for the Seabird maritime intelligence platform, inspired by the provided reference screenshots but not copying any existing game character. Stylized semi-realistic 3D painterly leader, upper-body to mid-thigh crop, three-quarter pose turned slightly toward the viewer, character placed slightly right-of-center as if standing beside an information panel, hands clearly visible, diplomatic command posture, slightly enlarged expressive head and eyes, polished sculpted face, heatrical side key light, warm highlights with cool soft shadows, subtle rim light, crisp silhouette, premium strategy game concept art. Transparent alpha background only, no environment; if any atmosphere is needed, use only faint edge shadow on the character, not a backdrop. Leave 8-10% transparent margin around the silhouette; do not crop head, hands, or props; suitable for a React Civ-style modal character header. Output as vertical 2:3 PNG, 1024x1536, alpha channel. Character: Nikolai Muravyov-Amursky (무라비요프-아무르스키). Role: 러시아 동시베리아 총독 · 블라디보스토크 창건 1809~1881. Type: respectful historical interpretation for a port or chokepoint region. Asset filename: region_vladivostok.png. Character-specific direction: Nikolai Muravyov-Amursky as a Russian Far East governor; 19th-century imperial military coat with fur collar and decorations; holding an Amur-region map and maritime survey instrument. Important: make the figure feel like a Civ loading-screen leader: not a normal portrait, not a photorealistic person, not a full-body fashion render. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Create a Civilization-style grand strategy leader loading-screen character asset for the Seabird maritime intelligence platform, inspired by the provided reference screenshots but not copying any existing game character. Stylized semi-realistic 3D painterly leader, upper-body to mid-thigh crop, three-quarter pose turned slightly toward the viewer, character placed slightly right-of-center as if standing beside an information panel, hands clearly visible, diplomatic command posture, slightly enlarged expressive head and eyes, polished sculpted face, heatrical side key light, warm highlights with cool soft shadows, subtle rim light, crisp silhouette, premium strategy game concept art. Transparent alpha background only, no environment; if any atmosphere is needed, use only faint edge shadow on the character, not a backdrop. Leave 8-10% transparent margin around the silhouette; do not crop head, hands, or props; suitable for a React Civ-style modal character header. Output as vertical 2:3 PNG, 1024x1536, alpha channel. Character: Parameswara (파라메스와라). Role: 말라카 술탄국 창건자 · 동남아 무역 제국 1344~1414. Type: respectful historical interpretation for a port or chokepoint region. Asset filename: region_portklang.png. Character-specific direction: Parameswara as founder of the Malacca Sultanate; royal Malay attire with gold songket, ceremonial kris, jeweled headgear; holding a strait trade seal and diplomatic scroll. Important: make the figure feel like a Civ loading-screen leader: not a normal portrait, not a photorealistic person, not a full-body fashion render. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Create a Civilization-style grand strategy leader loading-screen character asset for the Seabird maritime intelligence platform, inspired by the provided reference screenshots but not copying any existing game character. Stylized semi-realistic 3D painterly leader, upper-body to mid-thigh crop, three-quarter pose turned slightly toward the viewer, character placed slightly right-of-center as if standing beside an information panel, hands clearly visible, diplomatic command posture, slightly enlarged expressive head and eyes, polished sculpted face, heatrical side key light, warm highlights with cool soft shadows, subtle rim light, crisp silhouette, premium strategy game concept art. Transparent alpha background only, no environment; if any atmosphere is needed, use only faint edge shadow on the character, not a backdrop. Leave 8-10% transparent margin around the silhouette; do not crop head, hands, or props; suitable for a React Civ-style modal character header. Output as vertical 2:3 PNG, 1024x1536, alpha channel. Character: Chhatrapati Shivaji Maharaj (시바지 마하라지). Role: 마라타 제국 창건자 · 인도 최초 근대 해군 건설 1630~1680. Type: respectful historical interpretation for a port or chokepoint region. Asset filename: region_mumbai.png. Character-specific direction: Chhatrapati Shivaji Maharaj as a Maratha founder and naval builder; saffron turban, pearl ornaments, armored royal robe; holding a naval fort plan and curved sword lowered in ceremonial pose. Important: make the figure feel like a Civ loading-screen leader: not a normal portrait, not a photorealistic person, not a full-body fashion render. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Create a Civilization-style grand strategy leader loading-screen character asset for the Seabird maritime intelligence platform, inspired by the provided reference screenshots but not copying any existing game character. Stylized semi-realistic 3D painterly leader, upper-body to mid-thigh crop, three-quarter pose turned slightly toward the viewer, character placed slightly right-of-center as if standing beside an information panel, hands clearly visible, diplomatic command posture, slightly enlarged expressive head and eyes, polished sculpted face, heatrical side key light, warm highlights with cool soft shadows, subtle rim light, crisp silhouette, premium strategy game concept art. Transparent alpha background only, no environment; if any atmosphere is needed, use only faint edge shadow on the character, not a backdrop. Leave 8-10% transparent margin around the silhouette; do not crop head, hands, or props; suitable for a React Civ-style modal character header. Output as vertical 2:3 PNG, 1024x1536, alpha channel. Character: Henry the Lion (사자공 하인리히). Role: 작센·바이에른 공작 · 함부르크 항만 창건 1129~1195. Type: respectful historical interpretation for a port or chokepoint region. Asset filename: region_hamburg.png. Character-specific direction: Henry the Lion as a medieval Saxon-Bavarian duke; chainmail under a noble cloak, lion emblem brooch, golden hair; holding a city charter and harbor key. Important: make the figure feel like a Civ loading-screen leader: not a normal portrait, not a photorealistic person, not a full-body fashion render. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Create a Civilization-style grand strategy leader loading-screen character asset for the Seabird maritime intelligence platform, inspired by the provided reference screenshots but not copying any existing game character. Stylized semi-realistic 3D painterly leader, upper-body to mid-thigh crop, three-quarter pose turned slightly toward the viewer, character placed slightly right-of-center as if standing beside an information panel, hands clearly visible, diplomatic command posture, slightly enlarged expressive head and eyes, polished sculpted face, heatrical side key light, warm highlights with cool soft shadows, subtle rim light, crisp silhouette, premium strategy game concept art. Transparent alpha background only, no environment; if any atmosphere is needed, use only faint edge shadow on the character, not a backdrop. Leave 8-10% transparent margin around the silhouette; do not crop head, hands, or props; suitable for a React Civ-style modal character header. Output as vertical 2:3 PNG, 1024x1536, alpha channel. Character: Alexander Hamilton (알렉산더 해밀턴). Role: 미국 초대 재무장관 · 뉴욕 금융·무역 체계 설계 1755~1804. Type: respectful historical interpretation for a port or chokepoint region. Asset filename: region_newyork.png. Character-specific direction: Alexander Hamilton as an American finance architect; late-18th-century formal coat, waistcoat, cravat; holding a ledger of customs revenue and quill; intense, calculating gaze. Important: make the figure feel like a Civ loading-screen leader: not a normal portrait, not a photorealistic person, not a full-body fashion render. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Create a Civilization-style grand strategy leader loading-screen character asset for the Seabird maritime intelligence platform, inspired by the provided reference screenshots but not copying any existing game character. Stylized semi-realistic 3D painterly leader, upper-body to mid-thigh crop, three-quarter pose turned slightly toward the viewer, character placed slightly right-of-center as if standing beside an information panel, hands clearly visible, diplomatic command posture, slightly enlarged expressive head and eyes, polished sculpted face, heatrical side key light, warm highlights with cool soft shadows, subtle rim light, crisp silhouette, premium strategy game concept art. Transparent alpha background only, no environment; if any atmosphere is needed, use only faint edge shadow on the character, not a backdrop. Leave 8-10% transparent margin around the silhouette; do not crop head, hands, or props; suitable for a React Civ-style modal character header. Output as vertical 2:3 PNG, 1024x1536, alpha channel. Character: Sun Yat-sen (쑨원). Role: 중화민국 임시대총통 · 중국 근대 혁명의 아버지 1866~1925. Type: respectful historical interpretation for a port or chokepoint region. Asset filename: region_guangzhou.png. Character-specific direction: Sun Yat-sen as a modern revolutionary statesman; dark Zhongshan suit, composed posture; holding a republic document and maritime customs paper; idealistic determined expression. Important: make the figure feel like a Civ loading-screen leader: not a normal portrait, not a photorealistic person, not a full-body fashion render. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Create a Civilization-style grand strategy leader loading-screen character asset for the Seabird maritime intelligence platform, inspired by the provided reference screenshots but not copying any existing game character. Stylized semi-realistic 3D painterly leader, upper-body to mid-thigh crop, three-quarter pose turned slightly toward the viewer, character placed slightly right-of-center as if standing beside an information panel, hands clearly visible, diplomatic command posture, slightly enlarged expressive head and eyes, polished sculpted face, heatrical side key light, warm highlights with cool soft shadows, subtle rim light, crisp silhouette, premium strategy game concept art. Transparent alpha background only, no environment; if any atmosphere is needed, use only faint edge shadow on the character, not a backdrop. Leave 8-10% transparent margin around the silhouette; do not crop head, hands, or props; suitable for a React Civ-style modal character header. Output as vertical 2:3 PNG, 1024x1536, alpha channel. Character: Jiang Taigong (강태공). Role: 주나라 개국공신 · 제나라(산둥) 시조 기원전 11세기. Type: respectful historical interpretation for a port or chokepoint region. Asset filename: region_qingdao.png. Character-specific direction: Jiang Taigong as an ancient strategist; Zhou-era robes, white beard, serene eyes; holding a bamboo strategy slip and fishing rod fragment as symbolic prop. Important: make the figure feel like a Civ loading-screen leader: not a normal portrait, not a photorealistic person, not a full-body fashion render. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Create a Civilization-style grand strategy leader loading-screen character asset for the Seabird maritime intelligence platform, inspired by the provided reference screenshots but not copying any existing game character. Stylized semi-realistic 3D painterly leader, upper-body to mid-thigh crop, three-quarter pose turned slightly toward the viewer, character placed slightly right-of-center as if standing beside an information panel, hands clearly visible, diplomatic command posture, slightly enlarged expressive head and eyes, polished sculpted face, heatrical side key light, warm highlights with cool soft shadows, subtle rim light, crisp silhouette, premium strategy game concept art. Transparent alpha background only, no environment; if any atmosphere is needed, use only faint edge shadow on the character, not a backdrop. Leave 8-10% transparent margin around the silhouette; do not crop head, hands, or props; suitable for a React Civ-style modal character header. Output as vertical 2:3 PNG, 1024x1536, alpha channel. Character: Li Hongzhang (이홍장). Role: 청나라 직예총독 · 양무운동 주도 1823~1901. Type: respectful historical interpretation for a port or chokepoint region. Asset filename: region_tianjin.png. Character-specific direction: Li Hongzhang as a Qing reform statesman; formal Qing official robe with high-rank badge, mandarin hat, tired but shrewd gaze; holding a treaty folder and modernization blueprint. Important: make the figure feel like a Civ loading-screen leader: not a normal portrait, not a photorealistic person, not a full-body fashion render. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Create a Civilization-style grand strategy leader loading-screen character asset for the Seabird maritime intelligence platform, inspired by the provided reference screenshots but not copying any existing game character. Stylized semi-realistic 3D painterly leader, upper-body to mid-thigh crop, three-quarter pose turned slightly toward the viewer, character placed slightly right-of-center as if standing beside an information panel, hands clearly visible, diplomatic command posture, slightly enlarged expressive head and eyes, polished sculpted face, heatrical side key light, warm highlights with cool soft shadows, subtle rim light, crisp silhouette, premium strategy game concept art. Transparent alpha background only, no environment; if any atmosphere is needed, use only faint edge shadow on the character, not a backdrop. Leave 8-10% transparent margin around the silhouette; do not crop head, hands, or props; suitable for a React Civ-style modal character header. Output as vertical 2:3 PNG, 1024x1536, alpha channel. Character: Peter Paul Rubens (피터 폴 루벤스). Role: 앤트워프 출신 바로크 화가 · 외교관 1577~1640. Type: respectful historical interpretation for a port or chokepoint region. Asset filename: region_antwerp.png. Character-specific direction: Peter Paul Rubens as a Baroque painter-diplomat; black doublet, white collar, painterly cloak; holding a diplomatic letter and small brush; warm confident expression. Important: make the figure feel like a Civ loading-screen leader: not a normal portrait, not a photorealistic person, not a full-body fashion render. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Create a Civilization-style grand strategy leader loading-screen character asset for the Seabird maritime intelligence platform, inspired by the provided reference screenshots but not copying any existing game character. Stylized semi-realistic 3D painterly leader, upper-body to mid-thigh crop, three-quarter pose turned slightly toward the viewer, character placed slightly right-of-center as if standing beside an information panel, hands clearly visible, diplomatic command posture, slightly enlarged expressive head and eyes, polished sculpted face, heatrical side key light, warm highlights with cool soft shadows, subtle rim light, crisp silhouette, premium strategy game concept art. Transparent alpha background only, no environment; if any atmosphere is needed, use only faint edge shadow on the character, not a backdrop. Leave 8-10% transparent margin around the silhouette; do not crop head, hands, or props; suitable for a React Civ-style modal character header. Output as vertical 2:3 PNG, 1024x1536, alpha channel. Character: Sultan Abu Bakar of Johor (술탄 아부 바카르). Role: 조호르 술탄국 아버지 · 근대 조호르 창건 1833~1895. Type: respectful historical interpretation for a port or chokepoint region. Asset filename: region_tanjung_pelepas.png. Character-specific direction: Sultan Abu Bakar of Johor as a modernizing Malay ruler; elegant Johor royal attire with sash and medals, songkok; holding a port-development decree and maritime compass. Important: make the figure feel like a Civ loading-screen leader: not a normal portrait, not a photorealistic person, not a full-body fashion render. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Create a Civilization-style grand strategy leader loading-screen character asset for the Seabird maritime intelligence platform, inspired by the provided reference screenshots but not copying any existing game character. Stylized semi-realistic 3D painterly leader, upper-body to mid-thigh crop, three-quarter pose turned slightly toward the viewer, character placed slightly right-of-center as if standing beside an information panel, hands clearly visible, diplomatic command posture, slightly enlarged expressive head and eyes, polished sculpted face, heatrical side key light, warm highlights with cool soft shadows, subtle rim light, crisp silhouette, premium strategy game concept art. Transparent alpha background only, no environment; if any atmosphere is needed, use only faint edge shadow on the character, not a backdrop. Leave 8-10% transparent margin around the silhouette; do not crop head, hands, or props; suitable for a React Civ-style modal character header. Output as vertical 2:3 PNG, 1024x1536, alpha channel. Character: Koxinga (Zheng Chenggong) (정성공). Role: 명나라 충신 · 샤먼 기반 해상 왕국 건설 1624~1662. Type: respectful historical interpretation for a port or chokepoint region. Asset filename: region_xiamen.png. Character-specific direction: Koxinga / Zheng Chenggong as a Ming loyalist maritime commander; Chinese military robes with armor, red cape, determined gaze; holding a command fan and coastal fortress chart. Important: make the figure feel like a Civ loading-screen leader: not a normal portrait, not a photorealistic person, not a full-body fashion render. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Create a Civilization-style grand strategy leader loading-screen character asset for the Seabird maritime intelligence platform, inspired by the provided reference screenshots but not copying any existing game character. Stylized semi-realistic 3D painterly leader, upper-body to mid-thigh crop, three-quarter pose turned slightly toward the viewer, character placed slightly right-of-center as if standing beside an information panel, hands clearly visible, diplomatic command posture, slightly enlarged expressive head and eyes, polished sculpted face, heatrical side key light, warm highlights with cool soft shadows, subtle rim light, crisp silhouette, premium strategy game concept art. Transparent alpha background only, no environment; if any atmosphere is needed, use only faint edge shadow on the character, not a backdrop. Leave 8-10% transparent margin around the silhouette; do not crop head, hands, or props; suitable for a React Civ-style modal character header. Output as vertical 2:3 PNG, 1024x1536, alpha channel. Character: Lee Teng-hui (리덩후이). Role: 중화민국 제9대 총통 · 대만 민주화의 아버지 1923~2020. Type: respectful historical interpretation for a port or chokepoint region. Asset filename: region_kaohsiung.png. Character-specific direction: Lee Teng-hui as Taiwan democratization statesman; dark suit, modest tie, elder statesman expression; holding a democratic reform document and port-economy chart. Important: make the figure feel like a Civ loading-screen leader: not a normal portrait, not a photorealistic person, not a full-body fashion render. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Create a Civilization-style grand strategy leader loading-screen character asset for the Seabird maritime intelligence platform, inspired by the provided reference screenshots but not copying any existing game character. Stylized semi-realistic 3D painterly leader, upper-body to mid-thigh crop, three-quarter pose turned slightly toward the viewer, character placed slightly right-of-center as if standing beside an information panel, hands clearly visible, diplomatic command posture, slightly enlarged expressive head and eyes, polished sculpted face, heatrical side key light, warm highlights with cool soft shadows, subtle rim light, crisp silhouette, premium strategy game concept art. Transparent alpha background only, no environment; if any atmosphere is needed, use only faint edge shadow on the character, not a backdrop. Leave 8-10% transparent margin around the silhouette; do not crop head, hands, or props; suitable for a React Civ-style modal character header. Output as vertical 2:3 PNG, 1024x1536, alpha channel. Character: King Chulalongkorn (Rama V) (쭐랄롱꼰 대왕). Role: 태국 국왕 라마 5세 · 근대화 개혁 1853~1910. Type: respectful historical interpretation for a port or chokepoint region. Asset filename: region_laem_chabang.png. Character-specific direction: King Chulalongkorn / Rama V as a Thai modernizing monarch; ornate Thai royal military uniform with decorations and sash; holding a railway-port modernization plan. Important: make the figure feel like a Civ loading-screen leader: not a normal portrait, not a photorealistic person, not a full-body fashion render. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Create a Civilization-style grand strategy leader loading-screen character asset for the Seabird maritime intelligence platform, inspired by the provided reference screenshots but not copying any existing game character. Stylized semi-realistic 3D painterly leader, upper-body to mid-thigh crop, three-quarter pose turned slightly toward the viewer, character placed slightly right-of-center as if standing beside an information panel, hands clearly visible, diplomatic command posture, slightly enlarged expressive head and eyes, polished sculpted face, heatrical side key light, warm highlights with cool soft shadows, subtle rim light, crisp silhouette, premium strategy game concept art. Transparent alpha background only, no environment; if any atmosphere is needed, use only faint edge shadow on the character, not a backdrop. Leave 8-10% transparent margin around the silhouette; do not crop head, hands, or props; suitable for a React Civ-style modal character header. Output as vertical 2:3 PNG, 1024x1536, alpha channel. Character: Sukarno (수카르노). Role: 인도네시아 초대 대통령 · 독립운동 지도자 1901~1970. Type: respectful historical interpretation for a port or chokepoint region. Asset filename: region_jakarta.png. Character-specific direction: Sukarno as Indonesian independence leader; white military-style suit, black peci cap, charismatic expression; holding a proclamation folder and maritime archipelago map. Important: make the figure feel like a Civ loading-screen leader: not a normal portrait, not a photorealistic person, not a full-body fashion render. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Create a Civilization-style grand strategy leader loading-screen character asset for the Seabird maritime intelligence platform, inspired by the provided reference screenshots but not copying any existing game character. Stylized semi-realistic 3D painterly leader, upper-body to mid-thigh crop, three-quarter pose turned slightly toward the viewer, character placed slightly right-of-center as if standing beside an information panel, hands clearly visible, diplomatic command posture, slightly enlarged expressive head and eyes, polished sculpted face, heatrical side key light, warm highlights with cool soft shadows, subtle rim light, crisp silhouette, premium strategy game concept art. Transparent alpha background only, no environment; if any atmosphere is needed, use only faint edge shadow on the character, not a backdrop. Leave 8-10% transparent margin around the silhouette; do not crop head, hands, or props; suitable for a React Civ-style modal character header. Output as vertical 2:3 PNG, 1024x1536, alpha channel. Character: Parakramabahu I (파라크라마바후 1세). Role: 스리랑카 폴론나루와 왕국 왕 · 1123~1186. Type: respectful historical interpretation for a port or chokepoint region. Asset filename: region_colombo.png. Character-specific direction: Parakramabahu I as a Sri Lankan king; ancient Sinhalese royal attire with gold crown and layered ornaments; holding an irrigation-and-trade tablet and small ship charm. Important: make the figure feel like a Civ loading-screen leader: not a normal portrait, not a photorealistic person, not a full-body fashion render. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Create a Civilization-style grand strategy leader loading-screen character asset for the Seabird maritime intelligence platform, inspired by the provided reference screenshots but not copying any existing game character. Stylized semi-realistic 3D painterly leader, upper-body to mid-thigh crop, three-quarter pose turned slightly toward the viewer, character placed slightly right-of-center as if standing beside an information panel, hands clearly visible, diplomatic command posture, slightly enlarged expressive head and eyes, polished sculpted face, heatrical side key light, warm highlights with cool soft shadows, subtle rim light, crisp silhouette, premium strategy game concept art. Transparent alpha background only, no environment; if any atmosphere is needed, use only faint edge shadow on the character, not a backdrop. Leave 8-10% transparent margin around the silhouette; do not crop head, hands, or props; suitable for a React Civ-style modal character header. Output as vertical 2:3 PNG, 1024x1536, alpha channel. Character: James Oglethorpe (제임스 오글소프). Role: 조지아 식민지 창건자 · 사바나 도시 설계 1696~1785. Type: respectful historical interpretation for a port or chokepoint region. Asset filename: region_savannah.png. Character-specific direction: James Oglethorpe as Georgia colony founder; 18th-century British colonial officer attire, tricorn hat tucked under arm; holding a city grid plan and harbor charter. Important: make the figure feel like a Civ loading-screen leader: not a normal portrait, not a photorealistic person, not a full-body fashion render. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Create a Civilization-style grand strategy leader loading-screen character asset for the Seabird maritime intelligence platform, inspired by the provided reference screenshots but not copying any existing game character. Stylized semi-realistic 3D painterly leader, upper-body to mid-thigh crop, three-quarter pose turned slightly toward the viewer, character placed slightly right-of-center as if standing beside an information panel, hands clearly visible, diplomatic command posture, slightly enlarged expressive head and eyes, polished sculpted face, heatrical side key light, warm highlights with cool soft shadows, subtle rim light, crisp silhouette, premium strategy game concept art. Transparent alpha background only, no environment; if any atmosphere is needed, use only faint edge shadow on the character, not a backdrop. Leave 8-10% transparent margin around the silhouette; do not crop head, hands, or props; suitable for a React Civ-style modal character header. Output as vertical 2:3 PNG, 1024x1536, alpha channel. Character: Ho Chi Minh (호찌민). Role: 베트남 민주공화국 초대 주석 · 독립운동 지도자 1890~1969. Type: respectful historical interpretation for a port or chokepoint region. Asset filename: region_hochiminhcity.png. Character-specific direction: Ho Chi Minh as Vietnamese independence leader; simple khaki tunic, light beard, gentle but firm eyes; holding a folded independence document and river-port map. Important: make the figure feel like a Civ loading-screen leader: not a normal portrait, not a photorealistic person, not a full-body fashion render. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Create a Civilization-style grand strategy leader loading-screen character asset. Stylized semi-realistic 3D painterly leader, upper-body to mid-thigh crop, three-quarter pose turned slightly toward the viewer, character placed slightly right-of-center as if standing beside an information panel, hands clearly visible, diplomatic command posture, slightly enlarged expressive head and eyes, polished sculpted face, heatrical side key light, warm highlights with cool soft shadows, subtle rim light, crisp silhouette, premium strategy game concept art. Transparent alpha background only, no environment; if any atmosphere is needed, use only faint edge shadow on the character, not a backdrop. Leave 8-10% transparent margin around the silhouette; do not crop head, hands, or props; suitable for a React Civ-style modal character header. Output as vertical 2:3 PNG, 1024x1536, alpha channel. Character: Karim Al-Rashid (카림 알-라시드). Role: 원유 탱커 수석 엔지니어. Type: fictional modern maritime archetype. Asset filename: ship_tanker.png. Character-specific direction: Arab man in his late 40s, oil tanker chief engineer; navy coveralls upgraded into a ceremonial engineer coat with orange safety piping and brass pressure-gauge badges; short gray-flecked beard; one hand holds an oil-route clipboard, the other rests near a brass valve wheel prop. Important: make the figure feel like a Civ loading-screen leader: not a normal portrait, not a photorealistic person, not a full-body fashion render. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Create a Civilization-style grand strategy leader loading-screen character asset for the Seabird maritime intelligence platform, inspired by the provided reference screenshots but not copying any existing game character. Stylized semi-realistic 3D painterly leader, upper-body to mid-thigh crop, three-quarter pose turned slightly toward the viewer, character placed slightly right-of-center as if standing beside an information panel, hands clearly visible, diplomatic command posture, slightly enlarged expressive head and eyes, polished sculpted face, heatrical side key light, warm highlights with cool soft shadows, subtle rim light, crisp silhouette, premium strategy game concept art. Transparent alpha background only, no environment; if any atmosphere is needed, use only faint edge shadow on the character, not a backdrop. Leave 8-10% transparent margin around the silhouette; do not crop head, hands, or props; suitable for a React Civ-style modal character header. Output as vertical 2:3 PNG, 1024x1536, alpha channel. Character: Gamal Abdel Nasser (가말 압델 나세르). Role: 이집트 제2대 대통령 · 수에즈 국유화 1956. Type: respectful historical interpretation for a port or chokepoint region. Asset filename: region_suez.png. Character-specific direction: Gamal Abdel Nasser as a charismatic 1950s Egyptian statesman; khaki military dress uniform with restrained medals, strong brows, confident posture; holding a rolled Suez Canal treaty and brass canal ruler; subtle Egyptian eagle pin. Important: make the figure feel like a Civ loading-screen leader: not a normal portrait, not a photorealistic person, not a full-body fashion render. </t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>rich cloth folds, metal/jewelry highlights</t>
+  </si>
+  <si>
+    <t>Civ-like loading leader, mid-thigh crop, right-side placement, stylized 3D painterly realism, hands + props visible, transparent PNG</t>
+  </si>
+  <si>
+    <t>스타일키워드(Civ-like loading leader, mid-thigh crop, right-side placement, stylized 3D painterly realism, hands + props visible, transparent PNG)</t>
   </si>
 </sst>
 </file>
@@ -1136,7 +1146,61 @@
     <cellStyle name="표준" xfId="0" builtinId="0"/>
     <cellStyle name="Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="6">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -1235,10 +1299,10 @@
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="직함 / 역할"/>
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="성별"/>
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="국적 / 배경"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="스타일 키워드"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="스타일 키워드" dataDxfId="0" dataCellStyle="Normal"/>
     <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="개선 프롬프트 v3 (영어)"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="네거티브 프롬프트"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0100-00000C000000}" name="권장 생성 설정"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="네거티브 프롬프트" dataDxfId="2" dataCellStyle="Normal"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0100-00000C000000}" name="권장 생성 설정" dataDxfId="1" dataCellStyle="Normal"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1255,10 +1319,10 @@
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="직함 / 역할"/>
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0200-000007000000}" name="성별"/>
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0200-000008000000}" name="국적 / 배경"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0200-000009000000}" name="스타일 키워드" dataDxfId="0" dataCellStyle="Normal"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0200-000009000000}" name="스타일 키워드" dataDxfId="5" dataCellStyle="Normal"/>
     <tableColumn id="10" xr3:uid="{00000000-0010-0000-0200-00000A000000}" name="개선 프롬프트 v3 (영어)"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0200-00000B000000}" name="네거티브 프롬프트" dataDxfId="1" dataCellStyle="Normal"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0200-00000C000000}" name="권장 생성 설정" dataDxfId="2" dataCellStyle="Normal"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0200-00000B000000}" name="네거티브 프롬프트" dataDxfId="3" dataCellStyle="Normal"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0200-00000C000000}" name="권장 생성 설정" dataDxfId="4" dataCellStyle="Normal"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1473,40 +1537,40 @@
         <v>13</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>14</v>
+        <v>344</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="61.25" customHeight="1">
       <c r="A6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="61.25" customHeight="1">
       <c r="A7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C7" s="2" t="s">
         <v>19</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="61.25" customHeight="1">
       <c r="A8" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="C8" s="2" t="s">
         <v>22</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -1535,1602 +1599,1602 @@
   <sheetData>
     <row r="1" spans="1:12" ht="40" customHeight="1">
       <c r="A1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="146.75" customHeight="1">
       <c r="A2" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="I2" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="K2" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="L2" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="146.75" customHeight="1">
       <c r="A3" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C3" s="2" t="s">
+      <c r="F3" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="G3" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="H3" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>54</v>
-      </c>
       <c r="I3" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L3" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="146.75" customHeight="1">
       <c r="A4" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C4" s="2" t="s">
+      <c r="G4" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="H4" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>61</v>
-      </c>
       <c r="I4" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L4" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="L4" s="2" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="146.75" customHeight="1">
       <c r="A5" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>68</v>
-      </c>
       <c r="I5" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L5" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="146.75" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="I6" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L6" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="L6" s="2" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="146.75" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="I7" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L7" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="146.75" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="I8" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L8" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="146.75" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="I9" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L9" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="146.75" customHeight="1">
       <c r="A10" s="2" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
       <c r="I10" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L10" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="L10" s="2" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="146.75" customHeight="1">
       <c r="A11" s="2" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
       <c r="I11" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L11" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="L11" s="2" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="146.75" customHeight="1">
       <c r="A12" s="2" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
       <c r="I12" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L12" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="K12" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="L12" s="2" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="146.75" customHeight="1">
       <c r="A13" s="2" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>118</v>
+        <v>105</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>120</v>
+        <v>107</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
       <c r="I13" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L13" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="K13" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="L13" s="2" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="146.75" customHeight="1">
       <c r="A14" s="2" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
       <c r="I14" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L14" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="K14" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="L14" s="2" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="146.75" customHeight="1">
       <c r="A15" s="2" t="s">
-        <v>129</v>
+        <v>114</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>132</v>
+        <v>117</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>133</v>
+        <v>118</v>
       </c>
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
       <c r="I15" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L15" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="K15" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="L15" s="2" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="146.75" customHeight="1">
       <c r="A16" s="2" t="s">
-        <v>135</v>
+        <v>119</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>137</v>
+        <v>121</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
       <c r="I16" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L16" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="K16" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="L16" s="2" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="146.75" customHeight="1">
       <c r="A17" s="2" t="s">
-        <v>141</v>
+        <v>124</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>142</v>
+        <v>125</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>143</v>
+        <v>126</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>144</v>
+        <v>127</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>145</v>
+        <v>128</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>146</v>
+        <v>129</v>
       </c>
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
       <c r="I17" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L17" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="K17" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="L17" s="2" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="146.75" customHeight="1">
       <c r="A18" s="2" t="s">
-        <v>148</v>
+        <v>130</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>142</v>
+        <v>125</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>150</v>
+        <v>132</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>151</v>
+        <v>133</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>152</v>
+        <v>134</v>
       </c>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L18" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="K18" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="L18" s="2" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:12" ht="146.75" customHeight="1">
       <c r="A19" s="2" t="s">
-        <v>154</v>
+        <v>135</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>142</v>
+        <v>125</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>155</v>
+        <v>136</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>156</v>
+        <v>137</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>157</v>
+        <v>138</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>158</v>
+        <v>139</v>
       </c>
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
       <c r="I19" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L19" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="K19" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="L19" s="2" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="20" spans="1:12" ht="146.75" customHeight="1">
       <c r="A20" s="2" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="B20" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="D20" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="C20" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>162</v>
-      </c>
       <c r="E20" s="2" t="s">
-        <v>163</v>
+        <v>143</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>164</v>
+        <v>144</v>
       </c>
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
       <c r="I20" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L20" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="J20" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="K20" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="L20" s="2" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="21" spans="1:12" ht="146.75" customHeight="1">
       <c r="A21" s="2" t="s">
-        <v>166</v>
+        <v>145</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>142</v>
+        <v>125</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>167</v>
+        <v>146</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>168</v>
+        <v>147</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>169</v>
+        <v>148</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>170</v>
+        <v>149</v>
       </c>
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
       <c r="I21" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="K21" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L21" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="J21" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="K21" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="L21" s="2" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="22" spans="1:12" ht="146.75" customHeight="1">
       <c r="A22" s="2" t="s">
-        <v>172</v>
+        <v>150</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>142</v>
+        <v>125</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>173</v>
+        <v>151</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>174</v>
+        <v>152</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>175</v>
+        <v>153</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>176</v>
+        <v>154</v>
       </c>
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
       <c r="I22" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="K22" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L22" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="J22" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="K22" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="L22" s="2" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="23" spans="1:12" ht="146.75" customHeight="1">
       <c r="A23" s="2" t="s">
-        <v>178</v>
+        <v>155</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>142</v>
+        <v>125</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>179</v>
+        <v>156</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>180</v>
+        <v>157</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>181</v>
+        <v>158</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>182</v>
+        <v>159</v>
       </c>
       <c r="G23" s="2"/>
       <c r="H23" s="2"/>
       <c r="I23" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="K23" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L23" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="J23" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="K23" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="L23" s="2" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="24" spans="1:12" ht="146.75" customHeight="1">
       <c r="A24" s="2" t="s">
-        <v>184</v>
+        <v>160</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>142</v>
+        <v>125</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>185</v>
+        <v>161</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>186</v>
+        <v>162</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>187</v>
+        <v>163</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>188</v>
+        <v>164</v>
       </c>
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
       <c r="I24" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="K24" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L24" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="J24" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="K24" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="L24" s="2" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="25" spans="1:12" ht="146.75" customHeight="1">
       <c r="A25" s="2" t="s">
-        <v>190</v>
+        <v>165</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>142</v>
+        <v>125</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>191</v>
+        <v>166</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>192</v>
+        <v>167</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>193</v>
+        <v>168</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>194</v>
+        <v>169</v>
       </c>
       <c r="G25" s="2"/>
       <c r="H25" s="2"/>
       <c r="I25" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="K25" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L25" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="J25" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="K25" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="L25" s="2" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="26" spans="1:12" ht="146.75" customHeight="1">
       <c r="A26" s="2" t="s">
-        <v>196</v>
+        <v>170</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>142</v>
+        <v>125</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>197</v>
+        <v>171</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>198</v>
+        <v>172</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>199</v>
+        <v>173</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>200</v>
+        <v>174</v>
       </c>
       <c r="G26" s="2"/>
       <c r="H26" s="2"/>
       <c r="I26" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="K26" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L26" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="J26" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="K26" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="L26" s="2" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="27" spans="1:12" ht="146.75" customHeight="1">
       <c r="A27" s="2" t="s">
-        <v>202</v>
+        <v>175</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>142</v>
+        <v>125</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>203</v>
+        <v>176</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>204</v>
+        <v>177</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>205</v>
+        <v>178</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>206</v>
+        <v>179</v>
       </c>
       <c r="G27" s="2"/>
       <c r="H27" s="2"/>
       <c r="I27" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="K27" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L27" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="J27" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="K27" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="L27" s="2" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="28" spans="1:12" ht="146.75" customHeight="1">
       <c r="A28" s="2" t="s">
-        <v>208</v>
+        <v>180</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>142</v>
+        <v>125</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>209</v>
+        <v>181</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>210</v>
+        <v>182</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>211</v>
+        <v>183</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>212</v>
+        <v>184</v>
       </c>
       <c r="G28" s="2"/>
       <c r="H28" s="2"/>
       <c r="I28" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="K28" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L28" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="J28" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="K28" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="L28" s="2" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="29" spans="1:12" ht="146.75" customHeight="1">
       <c r="A29" s="2" t="s">
-        <v>214</v>
+        <v>185</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>142</v>
+        <v>125</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>215</v>
+        <v>186</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>216</v>
+        <v>187</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>217</v>
+        <v>188</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>218</v>
+        <v>189</v>
       </c>
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
       <c r="I29" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="K29" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L29" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="J29" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="K29" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="L29" s="2" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="30" spans="1:12" ht="146.75" customHeight="1">
       <c r="A30" s="2" t="s">
-        <v>220</v>
+        <v>190</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>142</v>
+        <v>125</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>221</v>
+        <v>191</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>222</v>
+        <v>192</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>223</v>
+        <v>193</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>224</v>
+        <v>194</v>
       </c>
       <c r="G30" s="2"/>
       <c r="H30" s="2"/>
       <c r="I30" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="K30" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L30" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="J30" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="K30" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="L30" s="2" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="31" spans="1:12" ht="146.75" customHeight="1">
       <c r="A31" s="2" t="s">
-        <v>226</v>
+        <v>195</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>142</v>
+        <v>125</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>227</v>
+        <v>196</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>228</v>
+        <v>197</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>229</v>
+        <v>198</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>230</v>
+        <v>199</v>
       </c>
       <c r="G31" s="2"/>
       <c r="H31" s="2"/>
       <c r="I31" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="J31" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="K31" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L31" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="J31" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="K31" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="L31" s="2" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="32" spans="1:12" ht="146.75" customHeight="1">
       <c r="A32" s="2" t="s">
-        <v>232</v>
+        <v>200</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>142</v>
+        <v>125</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>233</v>
+        <v>201</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>234</v>
+        <v>202</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>235</v>
+        <v>203</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>236</v>
+        <v>204</v>
       </c>
       <c r="G32" s="2"/>
       <c r="H32" s="2"/>
       <c r="I32" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="J32" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="K32" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L32" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="J32" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="K32" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="L32" s="2" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="33" spans="1:12" ht="146.75" customHeight="1">
       <c r="A33" s="2" t="s">
-        <v>238</v>
+        <v>205</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>142</v>
+        <v>125</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>239</v>
+        <v>206</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>240</v>
+        <v>207</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>241</v>
+        <v>208</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>242</v>
+        <v>209</v>
       </c>
       <c r="G33" s="2"/>
       <c r="H33" s="2"/>
       <c r="I33" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="J33" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="K33" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L33" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="J33" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="K33" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="L33" s="2" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="34" spans="1:12" ht="146.75" customHeight="1">
       <c r="A34" s="2" t="s">
-        <v>244</v>
+        <v>210</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>142</v>
+        <v>125</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>245</v>
+        <v>211</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>246</v>
+        <v>212</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>247</v>
+        <v>213</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>248</v>
+        <v>214</v>
       </c>
       <c r="G34" s="2"/>
       <c r="H34" s="2"/>
       <c r="I34" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="J34" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="K34" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L34" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="J34" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="K34" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="L34" s="2" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="35" spans="1:12" ht="146.75" customHeight="1">
       <c r="A35" s="2" t="s">
-        <v>250</v>
+        <v>215</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>142</v>
+        <v>125</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>251</v>
+        <v>216</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>252</v>
+        <v>217</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>253</v>
+        <v>218</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>254</v>
+        <v>219</v>
       </c>
       <c r="G35" s="2"/>
       <c r="H35" s="2"/>
       <c r="I35" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="J35" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="K35" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L35" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="J35" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="K35" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="L35" s="2" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="36" spans="1:12" ht="146.75" customHeight="1">
       <c r="A36" s="2" t="s">
-        <v>256</v>
+        <v>220</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>142</v>
+        <v>125</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>257</v>
+        <v>221</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>258</v>
+        <v>222</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>259</v>
+        <v>223</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>260</v>
+        <v>224</v>
       </c>
       <c r="G36" s="2"/>
       <c r="H36" s="2"/>
       <c r="I36" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="J36" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="K36" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L36" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="J36" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="K36" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="L36" s="2" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="37" spans="1:12" ht="146.75" customHeight="1">
       <c r="A37" s="2" t="s">
-        <v>262</v>
+        <v>225</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>142</v>
+        <v>125</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>263</v>
+        <v>226</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>264</v>
+        <v>227</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>265</v>
+        <v>228</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>266</v>
+        <v>229</v>
       </c>
       <c r="G37" s="2"/>
       <c r="H37" s="2"/>
       <c r="I37" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="J37" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="K37" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L37" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="J37" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="K37" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="L37" s="2" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="38" spans="1:12" ht="146.75" customHeight="1">
       <c r="A38" s="2" t="s">
-        <v>268</v>
+        <v>230</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>142</v>
+        <v>125</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>269</v>
+        <v>231</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>270</v>
+        <v>232</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>271</v>
+        <v>233</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>272</v>
+        <v>234</v>
       </c>
       <c r="G38" s="2"/>
       <c r="H38" s="2"/>
       <c r="I38" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="J38" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="K38" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L38" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="J38" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="K38" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="L38" s="2" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="39" spans="1:12" ht="146.75" customHeight="1">
       <c r="A39" s="2" t="s">
-        <v>274</v>
+        <v>235</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>142</v>
+        <v>125</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>275</v>
+        <v>236</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>276</v>
+        <v>237</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>277</v>
+        <v>238</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>278</v>
+        <v>239</v>
       </c>
       <c r="G39" s="2"/>
       <c r="H39" s="2"/>
       <c r="I39" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="J39" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="K39" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L39" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="J39" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="K39" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="L39" s="2" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="40" spans="1:12" ht="146.75" customHeight="1">
       <c r="A40" s="2" t="s">
-        <v>280</v>
+        <v>240</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>142</v>
+        <v>125</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>281</v>
+        <v>241</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>282</v>
+        <v>242</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>283</v>
+        <v>243</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>284</v>
+        <v>244</v>
       </c>
       <c r="G40" s="2"/>
       <c r="H40" s="2"/>
       <c r="I40" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="J40" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="K40" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L40" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="J40" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="K40" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="L40" s="2" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="41" spans="1:12" ht="146.75" customHeight="1">
       <c r="A41" s="2" t="s">
-        <v>286</v>
+        <v>245</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>142</v>
+        <v>125</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>287</v>
+        <v>246</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>288</v>
+        <v>247</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>289</v>
+        <v>248</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>290</v>
+        <v>249</v>
       </c>
       <c r="G41" s="2"/>
       <c r="H41" s="2"/>
       <c r="I41" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="J41" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="K41" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L41" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="J41" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="K41" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="L41" s="2" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="42" spans="1:12" ht="146.75" customHeight="1">
       <c r="A42" s="2" t="s">
-        <v>292</v>
+        <v>250</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>142</v>
+        <v>125</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>293</v>
+        <v>251</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>294</v>
+        <v>252</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>295</v>
+        <v>253</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>296</v>
+        <v>254</v>
       </c>
       <c r="G42" s="2"/>
       <c r="H42" s="2"/>
       <c r="I42" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="J42" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="K42" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L42" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="J42" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="K42" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="L42" s="2" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="43" spans="1:12" ht="146.75" customHeight="1">
       <c r="A43" s="2" t="s">
-        <v>298</v>
+        <v>255</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>142</v>
+        <v>125</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>299</v>
+        <v>256</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>300</v>
+        <v>257</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>301</v>
+        <v>258</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>302</v>
+        <v>259</v>
       </c>
       <c r="G43" s="2"/>
       <c r="H43" s="2"/>
       <c r="I43" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="J43" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="K43" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L43" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="J43" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="K43" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="L43" s="2" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="44" spans="1:12" ht="146.75" customHeight="1">
       <c r="A44" s="2" t="s">
-        <v>304</v>
+        <v>260</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>142</v>
+        <v>125</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>305</v>
+        <v>261</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>306</v>
+        <v>262</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>307</v>
+        <v>263</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>308</v>
+        <v>264</v>
       </c>
       <c r="G44" s="2"/>
       <c r="H44" s="2"/>
       <c r="I44" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="J44" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K44" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L44" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="J44" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="K44" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="L44" s="2" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="45" spans="1:12" ht="146.75" customHeight="1">
       <c r="A45" s="2" t="s">
-        <v>310</v>
+        <v>265</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>142</v>
+        <v>125</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>311</v>
+        <v>266</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>312</v>
+        <v>267</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>313</v>
+        <v>268</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>314</v>
+        <v>269</v>
       </c>
       <c r="G45" s="2"/>
       <c r="H45" s="2"/>
       <c r="I45" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="J45" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="K45" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L45" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="J45" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="K45" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="L45" s="2" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="46" spans="1:12" ht="146.75" customHeight="1">
       <c r="A46" s="2" t="s">
-        <v>316</v>
+        <v>270</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>142</v>
+        <v>125</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>317</v>
+        <v>271</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>318</v>
+        <v>272</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>319</v>
+        <v>273</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>320</v>
+        <v>274</v>
       </c>
       <c r="G46" s="2"/>
       <c r="H46" s="2"/>
       <c r="I46" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="J46" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="K46" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L46" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="J46" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="K46" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="L46" s="2" t="s">
-        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -3162,344 +3226,344 @@
   <sheetData>
     <row r="1" spans="1:12" ht="40" customHeight="1">
       <c r="A1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="L1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:12" ht="240">
+      <c r="A2" s="2" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" ht="270">
-      <c r="A2" s="2" t="s">
+      <c r="B2" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="H2" s="2" t="s">
-        <v>43</v>
-      </c>
       <c r="I2" s="2" t="s">
-        <v>44</v>
+        <v>346</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>45</v>
+        <v>297</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>340</v>
+        <v>296</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>47</v>
+        <v>293</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="146.75" customHeight="1">
       <c r="A3" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C3" s="2" t="s">
+      <c r="F3" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="G3" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="H3" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>54</v>
-      </c>
       <c r="I3" s="2" t="s">
-        <v>44</v>
+        <v>346</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>55</v>
+        <v>342</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>340</v>
+        <v>296</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>47</v>
+        <v>293</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="146.75" customHeight="1">
       <c r="A4" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C4" s="2" t="s">
+      <c r="G4" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="H4" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>61</v>
-      </c>
       <c r="I4" s="2" t="s">
-        <v>44</v>
+        <v>346</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>62</v>
+        <v>299</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>340</v>
+        <v>296</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>47</v>
+        <v>293</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="146.75" customHeight="1">
       <c r="A5" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>68</v>
-      </c>
       <c r="I5" s="2" t="s">
-        <v>44</v>
+        <v>346</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>69</v>
+        <v>300</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>340</v>
+        <v>296</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>47</v>
+        <v>293</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="146.75" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>44</v>
+        <v>346</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>76</v>
+        <v>301</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>340</v>
+        <v>296</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>47</v>
+        <v>293</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="146.75" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>44</v>
+        <v>346</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>83</v>
+        <v>302</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>340</v>
+        <v>296</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>47</v>
+        <v>293</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="146.75" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>44</v>
+        <v>346</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>90</v>
+        <v>303</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>340</v>
+        <v>296</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>47</v>
+        <v>293</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="146.75" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>44</v>
+        <v>346</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>97</v>
+        <v>304</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>340</v>
+        <v>296</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>47</v>
+        <v>293</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="146.75" customHeight="1"/>
@@ -3568,1298 +3632,1298 @@
   <sheetData>
     <row r="1" spans="1:12" ht="40" customHeight="1">
       <c r="A1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="146.75" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
       <c r="I2" s="2" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>104</v>
+        <v>343</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>341</v>
+        <v>294</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>343</v>
+        <v>293</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="146.75" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
       <c r="I3" s="2" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>110</v>
+        <v>306</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>341</v>
+        <v>294</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>343</v>
+        <v>293</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="146.75" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
       <c r="I4" s="2" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>116</v>
+        <v>307</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>341</v>
+        <v>294</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>343</v>
+        <v>293</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="146.75" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>118</v>
+        <v>105</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>120</v>
+        <v>107</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
       <c r="I5" s="2" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>122</v>
+        <v>308</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>341</v>
+        <v>294</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>343</v>
+        <v>293</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="146.75" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
       <c r="I6" s="2" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>128</v>
+        <v>309</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>341</v>
+        <v>294</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>343</v>
+        <v>293</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="146.75" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>129</v>
+        <v>114</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>132</v>
+        <v>117</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>133</v>
+        <v>118</v>
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
       <c r="I7" s="2" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>134</v>
+        <v>310</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>341</v>
+        <v>294</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>343</v>
+        <v>293</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="146.75" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>135</v>
+        <v>119</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>137</v>
+        <v>121</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
       <c r="I8" s="2" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>140</v>
+        <v>311</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>341</v>
+        <v>294</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>343</v>
+        <v>293</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="146.75" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>141</v>
+        <v>124</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>142</v>
+        <v>125</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>143</v>
+        <v>126</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>144</v>
+        <v>127</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>145</v>
+        <v>128</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>146</v>
+        <v>129</v>
       </c>
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
       <c r="I9" s="2" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>147</v>
+        <v>312</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>341</v>
+        <v>294</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>343</v>
+        <v>293</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="146.75" customHeight="1">
       <c r="A10" s="2" t="s">
-        <v>148</v>
+        <v>130</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>142</v>
+        <v>125</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>150</v>
+        <v>132</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>151</v>
+        <v>133</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>152</v>
+        <v>134</v>
       </c>
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
       <c r="I10" s="2" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>153</v>
+        <v>313</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>341</v>
+        <v>294</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>343</v>
+        <v>293</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="146.75" customHeight="1">
       <c r="A11" s="2" t="s">
-        <v>154</v>
+        <v>135</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>142</v>
+        <v>125</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>155</v>
+        <v>136</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>156</v>
+        <v>137</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>157</v>
+        <v>138</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>158</v>
+        <v>139</v>
       </c>
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
       <c r="I11" s="2" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>159</v>
+        <v>314</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>341</v>
+        <v>294</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>343</v>
+        <v>293</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="146.75" customHeight="1">
       <c r="A12" s="2" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>162</v>
-      </c>
       <c r="E12" s="2" t="s">
-        <v>163</v>
+        <v>143</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>164</v>
+        <v>144</v>
       </c>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
       <c r="I12" s="2" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>165</v>
+        <v>315</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>341</v>
+        <v>294</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>343</v>
+        <v>293</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="146.75" customHeight="1">
       <c r="A13" s="2" t="s">
-        <v>166</v>
+        <v>145</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>142</v>
+        <v>125</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>167</v>
+        <v>146</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>168</v>
+        <v>147</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>169</v>
+        <v>148</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>170</v>
+        <v>149</v>
       </c>
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
       <c r="I13" s="2" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>171</v>
+        <v>316</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>341</v>
+        <v>294</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>343</v>
+        <v>293</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="146.75" customHeight="1">
       <c r="A14" s="2" t="s">
-        <v>172</v>
+        <v>150</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>142</v>
+        <v>125</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>173</v>
+        <v>151</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>174</v>
+        <v>152</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>175</v>
+        <v>153</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>176</v>
+        <v>154</v>
       </c>
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
       <c r="I14" s="2" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>177</v>
+        <v>317</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>341</v>
+        <v>294</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>343</v>
+        <v>293</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="146.75" customHeight="1">
       <c r="A15" s="2" t="s">
-        <v>178</v>
+        <v>155</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>142</v>
+        <v>125</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>179</v>
+        <v>156</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>180</v>
+        <v>157</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>181</v>
+        <v>158</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>182</v>
+        <v>159</v>
       </c>
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
       <c r="I15" s="2" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>183</v>
+        <v>318</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>341</v>
+        <v>294</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>343</v>
+        <v>293</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="146.75" customHeight="1">
       <c r="A16" s="2" t="s">
-        <v>184</v>
+        <v>160</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>142</v>
+        <v>125</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>185</v>
+        <v>161</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>186</v>
+        <v>162</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>187</v>
+        <v>163</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>188</v>
+        <v>164</v>
       </c>
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
       <c r="I16" s="2" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>189</v>
+        <v>319</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>341</v>
+        <v>294</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>343</v>
+        <v>293</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="146.75" customHeight="1">
       <c r="A17" s="2" t="s">
-        <v>190</v>
+        <v>165</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>142</v>
+        <v>125</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>191</v>
+        <v>166</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>192</v>
+        <v>167</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>193</v>
+        <v>168</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>194</v>
+        <v>169</v>
       </c>
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
       <c r="I17" s="2" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>195</v>
+        <v>320</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>341</v>
+        <v>294</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>343</v>
+        <v>293</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="146.75" customHeight="1">
       <c r="A18" s="2" t="s">
-        <v>196</v>
+        <v>170</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>142</v>
+        <v>125</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>197</v>
+        <v>171</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>198</v>
+        <v>172</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>199</v>
+        <v>173</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>200</v>
+        <v>174</v>
       </c>
       <c r="G18" s="3"/>
       <c r="H18" s="3"/>
       <c r="I18" s="3" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="K18" s="3" t="s">
-        <v>341</v>
+        <v>321</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>294</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>343</v>
+        <v>293</v>
       </c>
     </row>
     <row r="19" spans="1:12" ht="146.75" customHeight="1">
       <c r="A19" s="2" t="s">
-        <v>202</v>
+        <v>175</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>142</v>
+        <v>125</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>203</v>
+        <v>176</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>204</v>
+        <v>177</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>205</v>
+        <v>178</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>206</v>
+        <v>179</v>
       </c>
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
       <c r="I19" s="2" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>207</v>
+        <v>322</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>341</v>
+        <v>294</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>343</v>
+        <v>293</v>
       </c>
     </row>
     <row r="20" spans="1:12" ht="146.75" customHeight="1">
       <c r="A20" s="2" t="s">
-        <v>208</v>
+        <v>180</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>142</v>
+        <v>125</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>209</v>
+        <v>181</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>210</v>
+        <v>182</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>211</v>
+        <v>183</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>212</v>
+        <v>184</v>
       </c>
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
       <c r="I20" s="2" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>213</v>
+        <v>323</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>341</v>
+        <v>294</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>343</v>
+        <v>293</v>
       </c>
     </row>
     <row r="21" spans="1:12" ht="146.75" customHeight="1">
       <c r="A21" s="2" t="s">
-        <v>214</v>
+        <v>185</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>142</v>
+        <v>125</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>215</v>
+        <v>186</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>216</v>
+        <v>187</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>217</v>
+        <v>188</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>218</v>
+        <v>189</v>
       </c>
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
       <c r="I21" s="2" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>219</v>
+        <v>324</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>341</v>
+        <v>294</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>343</v>
+        <v>293</v>
       </c>
     </row>
     <row r="22" spans="1:12" ht="146.75" customHeight="1">
       <c r="A22" s="2" t="s">
-        <v>220</v>
+        <v>190</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>142</v>
+        <v>125</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>221</v>
+        <v>191</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>222</v>
+        <v>192</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>223</v>
+        <v>193</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>224</v>
+        <v>194</v>
       </c>
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
       <c r="I22" s="2" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>341</v>
+        <v>294</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>343</v>
+        <v>293</v>
       </c>
     </row>
     <row r="23" spans="1:12" ht="146.75" customHeight="1">
       <c r="A23" s="2" t="s">
-        <v>226</v>
+        <v>195</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>142</v>
+        <v>125</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>227</v>
+        <v>196</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>228</v>
+        <v>197</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>229</v>
+        <v>198</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>230</v>
+        <v>199</v>
       </c>
       <c r="G23" s="2"/>
       <c r="H23" s="2"/>
       <c r="I23" s="2" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>231</v>
+        <v>326</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>341</v>
+        <v>294</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>343</v>
+        <v>293</v>
       </c>
     </row>
     <row r="24" spans="1:12" ht="146.75" customHeight="1">
       <c r="A24" s="2" t="s">
-        <v>232</v>
+        <v>200</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>142</v>
+        <v>125</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>233</v>
+        <v>201</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>234</v>
+        <v>202</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>235</v>
+        <v>203</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>236</v>
+        <v>204</v>
       </c>
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
       <c r="I24" s="2" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>237</v>
+        <v>327</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>341</v>
+        <v>294</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>343</v>
+        <v>293</v>
       </c>
     </row>
     <row r="25" spans="1:12" ht="146.75" customHeight="1">
       <c r="A25" s="2" t="s">
-        <v>238</v>
+        <v>205</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>142</v>
+        <v>125</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>239</v>
+        <v>206</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>240</v>
+        <v>207</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>241</v>
+        <v>208</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>242</v>
+        <v>209</v>
       </c>
       <c r="G25" s="2"/>
       <c r="H25" s="2"/>
       <c r="I25" s="2" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>243</v>
+        <v>328</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>341</v>
+        <v>294</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>343</v>
+        <v>293</v>
       </c>
     </row>
     <row r="26" spans="1:12" ht="146.75" customHeight="1">
       <c r="A26" s="2" t="s">
-        <v>244</v>
+        <v>210</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>142</v>
+        <v>125</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>245</v>
+        <v>211</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>246</v>
+        <v>212</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>247</v>
+        <v>213</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>248</v>
+        <v>214</v>
       </c>
       <c r="G26" s="2"/>
       <c r="H26" s="2"/>
-      <c r="I26" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="J26" s="2" t="s">
-        <v>249</v>
+      <c r="I26" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>329</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="L26" s="2" t="s">
-        <v>343</v>
+        <v>294</v>
+      </c>
+      <c r="L26" s="3" t="s">
+        <v>293</v>
       </c>
     </row>
     <row r="27" spans="1:12" ht="146.75" customHeight="1">
       <c r="A27" s="2" t="s">
-        <v>250</v>
+        <v>215</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>142</v>
+        <v>125</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>251</v>
+        <v>216</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>252</v>
+        <v>217</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>253</v>
+        <v>218</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>254</v>
+        <v>219</v>
       </c>
       <c r="G27" s="2"/>
       <c r="H27" s="2"/>
       <c r="I27" s="2" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>255</v>
+        <v>330</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>341</v>
+        <v>294</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>343</v>
+        <v>293</v>
       </c>
     </row>
     <row r="28" spans="1:12" ht="146.75" customHeight="1">
       <c r="A28" s="2" t="s">
-        <v>256</v>
+        <v>220</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>142</v>
+        <v>125</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>257</v>
+        <v>221</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>258</v>
+        <v>222</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>259</v>
+        <v>223</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>260</v>
+        <v>224</v>
       </c>
       <c r="G28" s="2"/>
       <c r="H28" s="2"/>
       <c r="I28" s="2" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>261</v>
+        <v>331</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>341</v>
+        <v>294</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>343</v>
+        <v>293</v>
       </c>
     </row>
     <row r="29" spans="1:12" ht="146.75" customHeight="1">
       <c r="A29" s="2" t="s">
-        <v>262</v>
+        <v>225</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>142</v>
+        <v>125</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>263</v>
+        <v>226</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>264</v>
+        <v>227</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>265</v>
+        <v>228</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>266</v>
+        <v>229</v>
       </c>
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
       <c r="I29" s="2" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>267</v>
+        <v>332</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>341</v>
+        <v>295</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>343</v>
+        <v>293</v>
       </c>
     </row>
     <row r="30" spans="1:12" ht="146.75" customHeight="1">
       <c r="A30" s="2" t="s">
-        <v>268</v>
+        <v>230</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>142</v>
+        <v>125</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>269</v>
+        <v>231</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>270</v>
+        <v>232</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>271</v>
+        <v>233</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>272</v>
+        <v>234</v>
       </c>
       <c r="G30" s="2"/>
       <c r="H30" s="2"/>
       <c r="I30" s="2" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>273</v>
+        <v>333</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>341</v>
+        <v>294</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>343</v>
+        <v>293</v>
       </c>
     </row>
     <row r="31" spans="1:12" ht="146.75" customHeight="1">
       <c r="A31" s="2" t="s">
-        <v>274</v>
+        <v>235</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>142</v>
+        <v>125</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>275</v>
+        <v>236</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>276</v>
+        <v>237</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>277</v>
+        <v>238</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>278</v>
+        <v>239</v>
       </c>
       <c r="G31" s="2"/>
       <c r="H31" s="2"/>
       <c r="I31" s="2" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>279</v>
+        <v>334</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>341</v>
+        <v>294</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>343</v>
+        <v>293</v>
       </c>
     </row>
     <row r="32" spans="1:12" ht="146.75" customHeight="1">
       <c r="A32" s="2" t="s">
-        <v>280</v>
+        <v>240</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>142</v>
+        <v>125</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>281</v>
+        <v>241</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>282</v>
+        <v>242</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>283</v>
+        <v>243</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>284</v>
+        <v>244</v>
       </c>
       <c r="G32" s="2"/>
       <c r="H32" s="2"/>
       <c r="I32" s="2" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>285</v>
+        <v>335</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>341</v>
+        <v>294</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>343</v>
+        <v>293</v>
       </c>
     </row>
     <row r="33" spans="1:12" ht="146.75" customHeight="1">
       <c r="A33" s="2" t="s">
-        <v>286</v>
+        <v>245</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>142</v>
+        <v>125</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>287</v>
+        <v>246</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>288</v>
+        <v>247</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>289</v>
+        <v>248</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>290</v>
+        <v>249</v>
       </c>
       <c r="G33" s="2"/>
       <c r="H33" s="2"/>
-      <c r="I33" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="J33" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="K33" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="L33" s="2" t="s">
-        <v>343</v>
+      <c r="I33" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="K33" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="L33" s="3" t="s">
+        <v>293</v>
       </c>
     </row>
     <row r="34" spans="1:12" ht="146.75" customHeight="1">
       <c r="A34" s="2" t="s">
-        <v>292</v>
+        <v>250</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>142</v>
+        <v>125</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>293</v>
+        <v>251</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>294</v>
+        <v>252</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>295</v>
+        <v>253</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>296</v>
+        <v>254</v>
       </c>
       <c r="G34" s="2"/>
       <c r="H34" s="2"/>
       <c r="I34" s="2" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>297</v>
+        <v>337</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>341</v>
+        <v>294</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>343</v>
+        <v>293</v>
       </c>
     </row>
     <row r="35" spans="1:12" ht="146.75" customHeight="1">
       <c r="A35" s="2" t="s">
-        <v>298</v>
+        <v>255</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>142</v>
+        <v>125</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>299</v>
+        <v>256</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>300</v>
+        <v>257</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>301</v>
+        <v>258</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>302</v>
+        <v>259</v>
       </c>
       <c r="G35" s="2"/>
       <c r="H35" s="2"/>
       <c r="I35" s="2" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>303</v>
+        <v>338</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>341</v>
+        <v>294</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>343</v>
+        <v>293</v>
       </c>
     </row>
     <row r="36" spans="1:12" ht="146.75" customHeight="1">
       <c r="A36" s="2" t="s">
-        <v>304</v>
+        <v>260</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>142</v>
+        <v>125</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>305</v>
+        <v>261</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>306</v>
+        <v>262</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>307</v>
+        <v>263</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>308</v>
+        <v>264</v>
       </c>
       <c r="G36" s="2"/>
       <c r="H36" s="2"/>
       <c r="I36" s="2" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>309</v>
+        <v>339</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>341</v>
+        <v>294</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>343</v>
+        <v>293</v>
       </c>
     </row>
     <row r="37" spans="1:12" ht="146.75" customHeight="1">
       <c r="A37" s="2" t="s">
-        <v>310</v>
+        <v>265</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>142</v>
+        <v>125</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>311</v>
+        <v>266</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>312</v>
+        <v>267</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>313</v>
+        <v>268</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>314</v>
+        <v>269</v>
       </c>
       <c r="G37" s="2"/>
       <c r="H37" s="2"/>
       <c r="I37" s="2" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>315</v>
+        <v>340</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>341</v>
+        <v>294</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>343</v>
+        <v>293</v>
       </c>
     </row>
     <row r="38" spans="1:12" ht="146.75" customHeight="1">
       <c r="A38" s="2" t="s">
-        <v>316</v>
+        <v>270</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>142</v>
+        <v>125</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>317</v>
+        <v>271</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>318</v>
+        <v>272</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>319</v>
+        <v>273</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>320</v>
+        <v>274</v>
       </c>
       <c r="G38" s="2"/>
       <c r="H38" s="2"/>
       <c r="I38" s="2" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>321</v>
+        <v>341</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>341</v>
+        <v>294</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>343</v>
+        <v>293</v>
       </c>
     </row>
     <row r="39" spans="1:12" ht="146.75" customHeight="1"/>
@@ -4891,74 +4955,74 @@
   <sheetData>
     <row r="1" spans="1:2" ht="45.25" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>322</v>
+        <v>275</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>323</v>
+        <v>276</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="45.25" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>324</v>
+        <v>277</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>325</v>
+        <v>278</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="45.25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>326</v>
+        <v>279</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>327</v>
+        <v>280</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="45.25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>328</v>
+        <v>281</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>329</v>
+        <v>282</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="45.25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>330</v>
+        <v>283</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>331</v>
+        <v>284</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="45.25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>332</v>
+        <v>285</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>333</v>
+        <v>286</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="45.25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>334</v>
+        <v>287</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>335</v>
+        <v>288</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="45.25" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>336</v>
+        <v>289</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>337</v>
+        <v>290</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="45.25" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>338</v>
+        <v>291</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>339</v>
+        <v>292</v>
       </c>
     </row>
   </sheetData>
